--- a/Business - Technology Services/SEZL.xlsx
+++ b/Business - Technology Services/SEZL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon\Documents\models\Business - Technology Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F39696-DB31-4D32-B92C-C13C9B23EA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8886DF-BBE2-4B29-8772-C2352894300F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="647" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="647" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="234">
   <si>
     <t>Price</t>
   </si>
@@ -1019,6 +1019,27 @@
   </si>
   <si>
     <t>Consensus</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Q127</t>
+  </si>
+  <si>
+    <t>Q227</t>
+  </si>
+  <si>
+    <t>Q327</t>
+  </si>
+  <si>
+    <t>Q427</t>
+  </si>
+  <si>
+    <t>FY27</t>
   </si>
 </sst>
 </file>
@@ -1770,7 +1791,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1807,17 +1828,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1934,26 +1951,19 @@
     <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2012,6 +2022,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -4853,7 +4889,7 @@
                   <c:v>271.12788999999998</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="#,##0">
-                  <c:v>449.16</c:v>
+                  <c:v>450.279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4988,7 +5024,7 @@
                   <c:v>0.70138919480622985</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.65663517685325568</c:v>
+                  <c:v>0.66076238043972535</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6078,7 +6114,7 @@
                   <c:v>77.581516999999963</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="#,##0">
-                  <c:v>122.25797999999999</c:v>
+                  <c:v>120.81471999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6202,7 +6238,7 @@
                   <c:v>9.3714636586471496</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.57586477717366691</c:v>
+                  <c:v>0.55726163488141212</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6921,16 +6957,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>8.0701849205519927E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>4.8590224904841231E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>5.3473343743460675E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>3.9014487804304464E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7651,7 +7687,7 @@
                   <c:v>-8.7600233879882611E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>5.3890279604810264E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15924,7 +15960,7 @@
       <c r="E2" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="56" t="s">
+      <c r="F2" s="52" t="s">
         <v>41</v>
       </c>
       <c r="G2" s="24"/>
@@ -15957,7 +15993,7 @@
       <c r="E3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="119">
+      <c r="F3" s="115">
         <v>0.62009999999999998</v>
       </c>
       <c r="H3" t="s">
@@ -15976,7 +16012,7 @@
       <c r="M3" t="s">
         <v>127</v>
       </c>
-      <c r="N3" s="36" t="s">
+      <c r="N3" s="35" t="s">
         <v>170</v>
       </c>
     </row>
@@ -15988,7 +16024,7 @@
       <c r="E4" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="119">
+      <c r="F4" s="115">
         <v>0.14199999999999999</v>
       </c>
       <c r="H4" t="s">
@@ -16176,7 +16212,7 @@
       <c r="E11" s="4"/>
       <c r="F11" s="27"/>
       <c r="I11" s="9"/>
-      <c r="J11" s="37"/>
+      <c r="J11" s="36"/>
       <c r="L11" s="4"/>
       <c r="N11" s="12"/>
     </row>
@@ -16198,9 +16234,9 @@
       <c r="B13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="34">
         <f>C6/Model!G32</f>
-        <v>64.942958607194598</v>
+        <v>64.176304565966205</v>
       </c>
       <c r="E13" s="4"/>
       <c r="J13" s="12"/>
@@ -16211,7 +16247,7 @@
       <c r="B14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="34">
         <f>C6/Model!H22</f>
         <v>21.384615384615387</v>
       </c>
@@ -16229,9 +16265,9 @@
       <c r="B15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="34">
         <f>C6/Model!I22</f>
-        <v>16.502283105022833</v>
+        <v>15.378723404255318</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -16240,7 +16276,7 @@
       </c>
       <c r="C16" s="5">
         <f>Model!H29</f>
-        <v>0.57586477717366691</v>
+        <v>0.55726163488141212</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -16249,40 +16285,40 @@
       </c>
       <c r="C17" s="5">
         <f>Model!I22/Model!H22-1</f>
-        <v>0.29585798816568043</v>
+        <v>0.39053254437869822</v>
       </c>
       <c r="E17" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="L17" s="146" t="s">
+      <c r="L17" s="137" t="s">
         <v>183</v>
       </c>
-      <c r="M17" s="147"/>
-      <c r="N17" s="148"/>
+      <c r="M17" s="138"/>
+      <c r="N17" s="139"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="45">
+      <c r="C18" s="41">
         <f>C14/(C16*100)</f>
-        <v>0.37134786207225007</v>
-      </c>
-      <c r="L18" s="149"/>
-      <c r="M18" s="150"/>
-      <c r="N18" s="151"/>
+        <v>0.38374461915301478</v>
+      </c>
+      <c r="L18" s="140"/>
+      <c r="M18" s="141"/>
+      <c r="N18" s="142"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="45">
+      <c r="C19" s="41">
         <f>C15/(C17*100)</f>
-        <v>0.55777716894977181</v>
-      </c>
-      <c r="L19" s="149"/>
-      <c r="M19" s="150"/>
-      <c r="N19" s="151"/>
+        <v>0.39378852353320432</v>
+      </c>
+      <c r="L19" s="140"/>
+      <c r="M19" s="141"/>
+      <c r="N19" s="142"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
@@ -16292,9 +16328,9 @@
         <f>Model!H4/Model!G4-1</f>
         <v>1.0343312650029444</v>
       </c>
-      <c r="L20" s="149"/>
-      <c r="M20" s="150"/>
-      <c r="N20" s="151"/>
+      <c r="L20" s="140"/>
+      <c r="M20" s="141"/>
+      <c r="N20" s="142"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
@@ -16302,11 +16338,11 @@
       </c>
       <c r="C21" s="5">
         <f>Model!I4/Model!H4-1</f>
-        <v>0.2601522842639592</v>
-      </c>
-      <c r="L21" s="149"/>
-      <c r="M21" s="150"/>
-      <c r="N21" s="151"/>
+        <v>0.27571466737910755</v>
+      </c>
+      <c r="L21" s="140"/>
+      <c r="M21" s="141"/>
+      <c r="N21" s="142"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
@@ -16316,9 +16352,9 @@
         <f>Model!G12</f>
         <v>82.245565999999968</v>
       </c>
-      <c r="L22" s="149"/>
-      <c r="M22" s="150"/>
-      <c r="N22" s="151"/>
+      <c r="L22" s="140"/>
+      <c r="M22" s="141"/>
+      <c r="N22" s="142"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
@@ -16328,9 +16364,9 @@
         <f>Model!G12</f>
         <v>82.245565999999968</v>
       </c>
-      <c r="L23" s="149"/>
-      <c r="M23" s="150"/>
-      <c r="N23" s="151"/>
+      <c r="L23" s="140"/>
+      <c r="M23" s="141"/>
+      <c r="N23" s="142"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
@@ -16340,9 +16376,9 @@
         <f>Model!V23</f>
         <v>0.8507226274872427</v>
       </c>
-      <c r="L24" s="149"/>
-      <c r="M24" s="150"/>
-      <c r="N24" s="151"/>
+      <c r="L24" s="140"/>
+      <c r="M24" s="141"/>
+      <c r="N24" s="142"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
@@ -16352,56 +16388,56 @@
         <f>Model!V24</f>
         <v>0.25149952244508123</v>
       </c>
-      <c r="L25" s="149"/>
-      <c r="M25" s="150"/>
-      <c r="N25" s="151"/>
+      <c r="L25" s="140"/>
+      <c r="M25" s="141"/>
+      <c r="N25" s="142"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="35">
+      <c r="C26" s="34">
         <f>C12/C23</f>
         <v>31.51238572545055</v>
       </c>
-      <c r="L26" s="149"/>
-      <c r="M26" s="150"/>
-      <c r="N26" s="151"/>
+      <c r="L26" s="140"/>
+      <c r="M26" s="141"/>
+      <c r="N26" s="142"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="116" t="s">
+      <c r="C27" s="112" t="s">
         <v>197</v>
       </c>
       <c r="E27" t="s">
         <v>64</v>
       </c>
-      <c r="L27" s="149"/>
-      <c r="M27" s="150"/>
-      <c r="N27" s="151"/>
+      <c r="L27" s="140"/>
+      <c r="M27" s="141"/>
+      <c r="N27" s="142"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="35">
+      <c r="C28" s="34">
         <f>C22/-Model!G13</f>
         <v>5.9764342126250147</v>
       </c>
       <c r="E28" t="s">
         <v>181</v>
       </c>
-      <c r="L28" s="152"/>
-      <c r="M28" s="153"/>
-      <c r="N28" s="154"/>
+      <c r="L28" s="143"/>
+      <c r="M28" s="144"/>
+      <c r="N28" s="145"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="35">
+      <c r="C29" s="34">
         <f>Model!V41/Model!V55</f>
         <v>3.5174777391044394</v>
       </c>
@@ -16413,7 +16449,7 @@
       <c r="B30" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C30" s="35">
+      <c r="C30" s="34">
         <f>(Model!V35+Model!V37)/Model!V55</f>
         <v>3.4378509961350385</v>
       </c>
@@ -16434,7 +16470,7 @@
       <c r="B32" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C32" s="35">
+      <c r="C32" s="34">
         <f>(Model!V47-Model!V55)/Model!V20</f>
         <v>7.6608829712683937</v>
       </c>
@@ -16446,7 +16482,7 @@
       <c r="B33" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="34">
         <f>Model!G3/Model!G47</f>
         <v>0.96226038494498256</v>
       </c>
@@ -16455,7 +16491,7 @@
       <c r="B34" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C34" s="37">
+      <c r="C34" s="36">
         <f>Model!G19/Model!G47</f>
         <v>0.27534467373694266</v>
       </c>
@@ -16464,7 +16500,7 @@
       <c r="B35" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C35" s="37">
+      <c r="C35" s="36">
         <f>Model!G19/Model!G62</f>
         <v>1.0892481418664739</v>
       </c>
@@ -16476,26 +16512,26 @@
       <c r="C36" s="22"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E41" s="52"/>
-      <c r="F41" s="52"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="55"/>
-      <c r="I41" s="55"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E42" s="53"/>
-      <c r="F42" s="54"/>
-      <c r="G42" s="54"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="50"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E43" s="53"/>
-      <c r="F43" s="54"/>
-      <c r="G43" s="54"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="50"/>
+      <c r="G43" s="50"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E44" s="53"/>
-      <c r="F44" s="54"/>
-      <c r="G44" s="54"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="50"/>
+      <c r="G44" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16508,22 +16544,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F7345E9-1C5F-45F5-BD7C-66FA029FFFF4}">
-  <dimension ref="A1:Z83"/>
+  <dimension ref="A1:AE83"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
     <col min="2" max="2" width="27.28515625" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="12"/>
+    <col min="7" max="7" width="11.42578125" style="156"/>
+    <col min="8" max="8" width="11.42578125" style="12"/>
     <col min="20" max="20" width="11.42578125" customWidth="1"/>
-    <col min="22" max="22" width="11.42578125" style="12"/>
+    <col min="22" max="22" width="11.42578125" style="156"/>
+    <col min="24" max="24" width="11.42578125" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>13</v>
       </c>
@@ -16536,15 +16574,18 @@
       <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="12" t="s">
         <v>59</v>
       </c>
       <c r="I2" t="s">
         <v>191</v>
       </c>
+      <c r="J2" t="s">
+        <v>233</v>
+      </c>
       <c r="L2" t="s">
         <v>8</v>
       </c>
@@ -16575,1092 +16616,1237 @@
       <c r="U2" t="s">
         <v>194</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="V2" s="156" t="s">
         <v>195</v>
       </c>
       <c r="W2" t="s">
         <v>196</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" s="12" t="s">
         <v>206</v>
       </c>
       <c r="Y2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z2" t="s">
+        <v>227</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>228</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>229</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>230</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>231</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="122">
+      <c r="C3" s="118">
         <f>49.659042+9.129231</f>
         <v>58.788273000000004</v>
       </c>
-      <c r="D3" s="122">
+      <c r="D3" s="118">
         <f>98.200184+16.616451</f>
         <v>114.81663499999999</v>
       </c>
-      <c r="E3" s="122">
+      <c r="E3" s="118">
         <v>125.570441</v>
       </c>
-      <c r="F3" s="122">
+      <c r="F3" s="118">
         <v>159.35677200000001</v>
       </c>
-      <c r="G3" s="123">
+      <c r="G3" s="158">
         <v>271.12788999999998</v>
       </c>
-      <c r="H3" s="144">
-        <f>H4</f>
-        <v>449.16</v>
-      </c>
-      <c r="I3" s="125">
+      <c r="H3" s="167">
+        <v>450.279</v>
+      </c>
+      <c r="I3" s="121">
         <f>I4</f>
-        <v>566.01</v>
+        <v>573</v>
       </c>
       <c r="L3" s="17">
         <v>34.673431000000001</v>
       </c>
-      <c r="M3" s="122">
+      <c r="M3" s="118">
         <v>34.937665000000003</v>
       </c>
-      <c r="N3" s="122">
+      <c r="N3" s="118">
         <v>40.844200999999998</v>
       </c>
-      <c r="O3" s="122">
+      <c r="O3" s="118">
         <f>F3-N3-M3-L3</f>
         <v>48.901474999999998</v>
       </c>
-      <c r="P3" s="122">
+      <c r="P3" s="118">
         <v>46.978634</v>
       </c>
-      <c r="Q3" s="122">
+      <c r="Q3" s="118">
         <v>55.968505</v>
       </c>
-      <c r="R3" s="122">
+      <c r="R3" s="118">
         <v>69.957690999999997</v>
       </c>
-      <c r="S3" s="122">
+      <c r="S3" s="118">
         <f>G3-R3-Q3-P3</f>
         <v>98.223059999999975</v>
       </c>
-      <c r="T3" s="122">
+      <c r="T3" s="118">
         <v>104.91200000000001</v>
       </c>
-      <c r="U3" s="122">
+      <c r="U3" s="118">
         <v>98.701999999999998</v>
       </c>
-      <c r="V3" s="123">
+      <c r="V3" s="158">
         <v>116.79600000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W3" s="116">
+        <f>H3-V3-U3-T3</f>
+        <v>129.869</v>
+      </c>
+      <c r="X3" s="120">
+        <v>135.53899999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="122"/>
-      <c r="D4" s="122"/>
-      <c r="E4" s="122"/>
-      <c r="F4" s="122"/>
-      <c r="G4" s="123">
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="158">
         <v>220.79</v>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="168">
         <v>449.16</v>
       </c>
-      <c r="I4" s="125">
-        <v>566.01</v>
+      <c r="I4" s="121">
+        <v>573</v>
+      </c>
+      <c r="J4" s="179">
+        <v>713</v>
       </c>
       <c r="L4" s="17"/>
-      <c r="M4" s="122"/>
-      <c r="N4" s="122"/>
-      <c r="O4" s="122"/>
-      <c r="P4" s="122"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="122">
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118"/>
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118">
         <v>52.63</v>
       </c>
-      <c r="S4" s="122">
+      <c r="S4" s="176">
         <v>65.180000000000007</v>
       </c>
-      <c r="T4" s="122"/>
-      <c r="U4" s="122">
+      <c r="T4" s="176"/>
+      <c r="U4" s="176">
         <v>93.33</v>
       </c>
-      <c r="V4" s="123">
+      <c r="V4" s="177">
         <v>104.7</v>
       </c>
-      <c r="W4" s="122">
+      <c r="W4" s="176">
         <v>128.91</v>
       </c>
-      <c r="X4" s="122">
+      <c r="X4" s="178">
         <v>128.1</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y4" s="179">
+        <v>132</v>
+      </c>
+      <c r="Z4" s="179">
+        <v>149</v>
+      </c>
+      <c r="AA4" s="179">
+        <v>165</v>
+      </c>
+      <c r="AB4" s="179">
+        <v>157</v>
+      </c>
+      <c r="AC4" s="179">
+        <v>165</v>
+      </c>
+      <c r="AD4" s="179">
+        <v>184</v>
+      </c>
+      <c r="AE4" s="179">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>160</v>
       </c>
-      <c r="C5" s="122">
+      <c r="C5" s="118">
         <v>30.689461999999999</v>
       </c>
-      <c r="D5" s="122">
+      <c r="D5" s="118">
         <v>56.831367999999998</v>
       </c>
-      <c r="E5" s="122">
+      <c r="E5" s="118">
         <v>51.217083000000002</v>
       </c>
-      <c r="F5" s="122">
+      <c r="F5" s="118">
         <v>46.373914999999997</v>
       </c>
-      <c r="G5" s="123">
+      <c r="G5" s="158">
         <v>51.764963999999999</v>
       </c>
-      <c r="H5" s="39"/>
+      <c r="H5" s="169">
+        <v>54.825000000000003</v>
+      </c>
       <c r="L5" s="17">
         <v>11.57399</v>
       </c>
-      <c r="M5" s="122">
+      <c r="M5" s="118">
         <v>12.017071</v>
       </c>
-      <c r="N5" s="122">
+      <c r="N5" s="118">
         <v>11.079174</v>
       </c>
-      <c r="O5" s="122">
+      <c r="O5" s="118">
         <f t="shared" ref="O5:O10" si="0">F5-N5-M5-L5</f>
         <v>11.703679999999993</v>
       </c>
-      <c r="P5" s="122">
+      <c r="P5" s="118">
         <v>11.025040000000001</v>
       </c>
-      <c r="Q5" s="122">
+      <c r="Q5" s="118">
         <v>12.736523</v>
       </c>
-      <c r="R5" s="122">
+      <c r="R5" s="118">
         <v>13.423723000000001</v>
       </c>
-      <c r="S5" s="122">
+      <c r="S5" s="118">
         <f t="shared" ref="S5:S10" si="1">G5-R5-Q5-P5</f>
         <v>14.579677999999998</v>
       </c>
-      <c r="T5" s="122">
+      <c r="T5" s="118">
         <v>15.048</v>
       </c>
-      <c r="U5" s="122">
+      <c r="U5" s="118">
         <v>11.680999999999999</v>
       </c>
-      <c r="V5" s="123">
+      <c r="V5" s="158">
         <v>14.32</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W5" s="175">
+        <f t="shared" ref="W5:W10" si="2">H5-V5-U5-T5</f>
+        <v>13.776000000000005</v>
+      </c>
+      <c r="X5" s="119">
+        <v>14.667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>159</v>
       </c>
-      <c r="C6" s="122">
+      <c r="C6" s="118">
         <v>22.489626000000001</v>
       </c>
-      <c r="D6" s="122">
+      <c r="D6" s="118">
         <v>43.476143</v>
       </c>
-      <c r="E6" s="122">
+      <c r="E6" s="118">
         <v>40.776825000000002</v>
       </c>
-      <c r="F6" s="122">
+      <c r="F6" s="118">
         <v>39.207768000000002</v>
       </c>
-      <c r="G6" s="123">
+      <c r="G6" s="158">
         <v>51.364347000000002</v>
       </c>
-      <c r="H6" s="39"/>
+      <c r="H6" s="169">
+        <v>65.960999999999999</v>
+      </c>
       <c r="L6" s="17">
         <v>8.2385859999999997</v>
       </c>
-      <c r="M6" s="122">
+      <c r="M6" s="118">
         <v>7.9459479999999996</v>
       </c>
-      <c r="N6" s="122">
+      <c r="N6" s="118">
         <v>9.9368040000000004</v>
       </c>
-      <c r="O6" s="122">
+      <c r="O6" s="118">
         <f t="shared" si="0"/>
         <v>13.086429999999998</v>
       </c>
-      <c r="P6" s="122">
+      <c r="P6" s="118">
         <v>11.787146</v>
       </c>
-      <c r="Q6" s="122">
+      <c r="Q6" s="118">
         <v>10.741618000000001</v>
       </c>
-      <c r="R6" s="122">
+      <c r="R6" s="118">
         <v>12.761438</v>
       </c>
-      <c r="S6" s="122">
+      <c r="S6" s="118">
         <f t="shared" si="1"/>
         <v>16.074145000000001</v>
       </c>
-      <c r="T6" s="122">
+      <c r="T6" s="118">
         <v>15.317</v>
       </c>
-      <c r="U6" s="122">
+      <c r="U6" s="118">
         <v>14.243</v>
       </c>
-      <c r="V6" s="123">
+      <c r="V6" s="158">
         <v>17.434999999999999</v>
       </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W6" s="175">
+        <f t="shared" si="2"/>
+        <v>18.965999999999994</v>
+      </c>
+      <c r="X6" s="119">
+        <v>18.52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>158</v>
       </c>
-      <c r="C7" s="122">
+      <c r="C7" s="118">
         <v>2.454113</v>
       </c>
-      <c r="D7" s="122">
+      <c r="D7" s="118">
         <v>5.5498440000000002</v>
       </c>
-      <c r="E7" s="122">
+      <c r="E7" s="118">
         <v>8.1900220000000008</v>
       </c>
-      <c r="F7" s="122">
+      <c r="F7" s="118">
         <v>7.8159150000000004</v>
       </c>
-      <c r="G7" s="123">
+      <c r="G7" s="158">
         <v>9.5951059999999995</v>
       </c>
-      <c r="H7" s="39"/>
+      <c r="H7" s="169">
+        <v>14.441000000000001</v>
+      </c>
       <c r="L7" s="17">
         <v>1.7491760000000001</v>
       </c>
-      <c r="M7" s="122">
+      <c r="M7" s="118">
         <v>1.9036299999999999</v>
       </c>
-      <c r="N7" s="122">
+      <c r="N7" s="118">
         <v>2.0025149999999998</v>
       </c>
-      <c r="O7" s="122">
+      <c r="O7" s="118">
         <f t="shared" si="0"/>
         <v>2.1605940000000006</v>
       </c>
-      <c r="P7" s="122">
+      <c r="P7" s="118">
         <v>2.1571720000000001</v>
       </c>
-      <c r="Q7" s="122">
+      <c r="Q7" s="118">
         <v>2.1802329999999999</v>
       </c>
-      <c r="R7" s="122">
+      <c r="R7" s="118">
         <v>2.3864899999999998</v>
       </c>
-      <c r="S7" s="122">
+      <c r="S7" s="118">
         <f t="shared" si="1"/>
         <v>2.8712109999999997</v>
       </c>
-      <c r="T7" s="122">
+      <c r="T7" s="118">
         <v>3.3740000000000001</v>
       </c>
-      <c r="U7" s="122">
+      <c r="U7" s="118">
         <v>3.4279999999999999</v>
       </c>
-      <c r="V7" s="123">
+      <c r="V7" s="158">
         <v>3.7050000000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W7" s="175">
+        <f t="shared" si="2"/>
+        <v>3.9340000000000006</v>
+      </c>
+      <c r="X7" s="119">
+        <v>4.415</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>157</v>
       </c>
-      <c r="C8" s="122">
+      <c r="C8" s="118">
         <v>4.2749290000000002</v>
       </c>
-      <c r="D8" s="122">
+      <c r="D8" s="118">
         <v>9.2518539999999998</v>
       </c>
-      <c r="E8" s="122">
+      <c r="E8" s="118">
         <v>18.972024999999999</v>
       </c>
-      <c r="F8" s="122">
+      <c r="F8" s="118">
         <v>11.984019</v>
       </c>
-      <c r="G8" s="123">
+      <c r="G8" s="158">
         <v>9.7397629999999999</v>
       </c>
-      <c r="H8" s="39"/>
+      <c r="H8" s="169">
+        <v>32.191000000000003</v>
+      </c>
       <c r="L8" s="17">
         <v>3.1991740000000002</v>
       </c>
-      <c r="M8" s="122">
+      <c r="M8" s="118">
         <v>3.3136619999999999</v>
       </c>
-      <c r="N8" s="122">
+      <c r="N8" s="118">
         <v>3.6153390000000001</v>
       </c>
-      <c r="O8" s="122">
+      <c r="O8" s="118">
         <f t="shared" si="0"/>
         <v>1.8558439999999994</v>
       </c>
-      <c r="P8" s="122">
+      <c r="P8" s="118">
         <v>0.65487499999999998</v>
       </c>
-      <c r="Q8" s="122">
+      <c r="Q8" s="118">
         <v>0.995089</v>
       </c>
-      <c r="R8" s="122">
+      <c r="R8" s="118">
         <v>2.7256149999999999</v>
       </c>
-      <c r="S8" s="122">
+      <c r="S8" s="118">
         <f t="shared" si="1"/>
         <v>5.3641840000000007</v>
       </c>
-      <c r="T8" s="122">
+      <c r="T8" s="118">
         <v>5.3460000000000001</v>
       </c>
-      <c r="U8" s="122">
+      <c r="U8" s="118">
         <v>8.7720000000000002</v>
       </c>
-      <c r="V8" s="123">
+      <c r="V8" s="158">
         <v>8.7750000000000004</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W8" s="175">
+        <f t="shared" si="2"/>
+        <v>9.2980000000000036</v>
+      </c>
+      <c r="X8" s="119">
+        <v>11.246</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="122">
+      <c r="C9" s="118">
         <v>7.2145349999999997</v>
       </c>
-      <c r="D9" s="122">
+      <c r="D9" s="118">
         <v>15.768583</v>
       </c>
-      <c r="E9" s="122">
+      <c r="E9" s="118">
         <v>16.411912000000001</v>
       </c>
-      <c r="F9" s="122">
+      <c r="F9" s="118">
         <v>8.5877809999999997</v>
       </c>
-      <c r="G9" s="123">
+      <c r="G9" s="158">
         <v>11.403468</v>
       </c>
-      <c r="H9" s="39"/>
+      <c r="H9" s="169">
+        <v>16.774000000000001</v>
+      </c>
       <c r="L9" s="17">
         <v>2.7982100000000001</v>
       </c>
-      <c r="M9" s="122">
+      <c r="M9" s="118">
         <v>1.6976290000000001</v>
       </c>
-      <c r="N9" s="122">
+      <c r="N9" s="118">
         <v>2.1840760000000001</v>
       </c>
-      <c r="O9" s="122">
+      <c r="O9" s="118">
         <f t="shared" si="0"/>
         <v>1.9078659999999994</v>
       </c>
-      <c r="P9" s="122">
+      <c r="P9" s="118">
         <v>2.3797779999999999</v>
       </c>
-      <c r="Q9" s="122">
+      <c r="Q9" s="118">
         <v>2.521782</v>
       </c>
-      <c r="R9" s="122">
+      <c r="R9" s="118">
         <v>2.4169510000000001</v>
       </c>
-      <c r="S9" s="122">
+      <c r="S9" s="118">
         <f t="shared" si="1"/>
         <v>4.0849569999999993</v>
       </c>
-      <c r="T9" s="122">
+      <c r="T9" s="118">
         <v>3.1309999999999998</v>
       </c>
-      <c r="U9" s="122">
+      <c r="U9" s="118">
         <v>3.8460000000000001</v>
       </c>
-      <c r="V9" s="123">
+      <c r="V9" s="158">
         <v>4.8230000000000004</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W9" s="175">
+        <f t="shared" si="2"/>
+        <v>4.9740000000000002</v>
+      </c>
+      <c r="X9" s="119">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>156</v>
       </c>
-      <c r="C10" s="122">
+      <c r="C10" s="118">
         <v>19.587917999999998</v>
       </c>
-      <c r="D10" s="122">
+      <c r="D10" s="118">
         <v>52.621682</v>
       </c>
-      <c r="E10" s="122">
+      <c r="E10" s="118">
         <v>29.437179</v>
       </c>
-      <c r="F10" s="122">
+      <c r="F10" s="118">
         <v>23.186972999999998</v>
       </c>
-      <c r="G10" s="123">
+      <c r="G10" s="158">
         <v>55.014676000000001</v>
       </c>
-      <c r="H10" s="9"/>
+      <c r="H10" s="14">
+        <v>89.298000000000002</v>
+      </c>
       <c r="L10" s="17">
         <v>1.694364</v>
       </c>
-      <c r="M10" s="122">
+      <c r="M10" s="118">
         <v>4.2964339999999996</v>
       </c>
-      <c r="N10" s="122">
+      <c r="N10" s="118">
         <v>6.6765480000000004</v>
       </c>
-      <c r="O10" s="122">
+      <c r="O10" s="118">
         <f t="shared" si="0"/>
         <v>10.519626999999998</v>
       </c>
-      <c r="P10" s="122">
+      <c r="P10" s="118">
         <v>5.1399660000000003</v>
       </c>
-      <c r="Q10" s="122">
+      <c r="Q10" s="118">
         <v>10.09388</v>
       </c>
-      <c r="R10" s="122">
+      <c r="R10" s="118">
         <v>15.402303</v>
       </c>
-      <c r="S10" s="122">
+      <c r="S10" s="118">
         <f t="shared" si="1"/>
         <v>24.378527000000005</v>
       </c>
-      <c r="T10" s="122">
+      <c r="T10" s="118">
         <v>12.801</v>
       </c>
-      <c r="U10" s="122">
+      <c r="U10" s="118">
         <v>20.646000000000001</v>
       </c>
-      <c r="V10" s="123">
+      <c r="V10" s="158">
         <v>32.177</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W10" s="175">
+        <f t="shared" si="2"/>
+        <v>23.673999999999999</v>
+      </c>
+      <c r="X10" s="119">
+        <v>13.675000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>155</v>
       </c>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122">
+      <c r="C11" s="118"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="118">
         <v>-11</v>
       </c>
-      <c r="F11" s="122"/>
-      <c r="G11" s="123"/>
-      <c r="H11" s="39"/>
+      <c r="F11" s="118"/>
+      <c r="G11" s="158"/>
+      <c r="H11" s="169"/>
       <c r="L11" s="17"/>
-      <c r="M11" s="122"/>
-      <c r="N11" s="122"/>
-      <c r="O11" s="122"/>
-      <c r="P11" s="122"/>
-      <c r="Q11" s="122"/>
-      <c r="R11" s="122"/>
-      <c r="S11" s="122"/>
-      <c r="T11" s="122"/>
-      <c r="U11" s="122"/>
-      <c r="V11" s="123"/>
-    </row>
-    <row r="12" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M11" s="118"/>
+      <c r="N11" s="118"/>
+      <c r="O11" s="118"/>
+      <c r="P11" s="118"/>
+      <c r="Q11" s="118"/>
+      <c r="R11" s="118"/>
+      <c r="S11" s="118"/>
+      <c r="T11" s="118"/>
+      <c r="U11" s="118"/>
+      <c r="V11" s="158"/>
+      <c r="X11" s="119"/>
+    </row>
+    <row r="12" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="120">
-        <f t="shared" ref="C12:E12" si="2">C3-SUM(C5:C11)</f>
+      <c r="C12" s="116">
+        <f t="shared" ref="C12:E12" si="3">C3-SUM(C5:C11)</f>
         <v>-27.922309999999996</v>
       </c>
-      <c r="D12" s="120">
-        <f t="shared" si="2"/>
+      <c r="D12" s="116">
+        <f t="shared" si="3"/>
         <v>-68.682839000000001</v>
       </c>
-      <c r="E12" s="120">
-        <f t="shared" si="2"/>
+      <c r="E12" s="116">
+        <f t="shared" si="3"/>
         <v>-28.434604999999991</v>
       </c>
-      <c r="F12" s="120">
+      <c r="F12" s="116">
         <f>F3-SUM(F5:F11)</f>
         <v>22.200400999999999</v>
       </c>
-      <c r="G12" s="124">
+      <c r="G12" s="159">
         <f>G3-SUM(G5:G11)</f>
         <v>82.245565999999968</v>
       </c>
-      <c r="H12" s="10">
-        <f>H3-SUM(H8:H11)</f>
-        <v>449.16</v>
+      <c r="H12" s="13">
+        <f>H3-SUM(H5:H11)</f>
+        <v>176.78899999999999</v>
       </c>
       <c r="I12" s="10">
         <f>I3-SUM(I8:I11)</f>
-        <v>566.01</v>
+        <v>573</v>
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
       <c r="L12" s="2">
-        <f t="shared" ref="L12" si="3">L3-SUM(L5:L11)</f>
+        <f t="shared" ref="L12" si="4">L3-SUM(L5:L11)</f>
         <v>5.4199310000000018</v>
       </c>
-      <c r="M12" s="120">
+      <c r="M12" s="116">
         <f>M3-SUM(M5:M11)</f>
         <v>3.7632910000000024</v>
       </c>
-      <c r="N12" s="120">
-        <f t="shared" ref="N12" si="4">N3-SUM(N5:N11)</f>
+      <c r="N12" s="116">
+        <f t="shared" ref="N12" si="5">N3-SUM(N5:N11)</f>
         <v>5.3497449999999986</v>
       </c>
-      <c r="O12" s="120">
-        <f t="shared" ref="O12" si="5">O3-SUM(O5:O11)</f>
+      <c r="O12" s="116">
+        <f t="shared" ref="O12" si="6">O3-SUM(O5:O11)</f>
         <v>7.6674340000000072</v>
       </c>
-      <c r="P12" s="120">
-        <f t="shared" ref="P12" si="6">P3-SUM(P5:P11)</f>
+      <c r="P12" s="116">
+        <f t="shared" ref="P12" si="7">P3-SUM(P5:P11)</f>
         <v>13.834657</v>
       </c>
-      <c r="Q12" s="120">
-        <f t="shared" ref="Q12" si="7">Q3-SUM(Q5:Q11)</f>
+      <c r="Q12" s="116">
+        <f t="shared" ref="Q12" si="8">Q3-SUM(Q5:Q11)</f>
         <v>16.699379999999998</v>
       </c>
-      <c r="R12" s="120">
+      <c r="R12" s="116">
         <f>R3-SUM(R5:R11)</f>
         <v>20.841171000000003</v>
       </c>
-      <c r="S12" s="120">
+      <c r="S12" s="116">
         <f>S3-SUM(S5:S11)</f>
         <v>30.870357999999968</v>
       </c>
-      <c r="T12" s="120">
+      <c r="T12" s="116">
         <f>T3-SUM(T5:T11)</f>
         <v>49.894999999999996</v>
       </c>
-      <c r="U12" s="120">
-        <f t="shared" ref="U12:Y12" si="8">U3-SUM(U5:U11)</f>
+      <c r="U12" s="116">
+        <f t="shared" ref="U12:Y12" si="9">U3-SUM(U5:U11)</f>
         <v>36.085999999999999</v>
       </c>
-      <c r="V12" s="124">
-        <f t="shared" si="8"/>
+      <c r="V12" s="159">
+        <f t="shared" si="9"/>
         <v>35.561000000000007</v>
       </c>
-      <c r="W12" s="120">
-        <f t="shared" si="8"/>
+      <c r="W12" s="116">
+        <f t="shared" si="9"/>
+        <v>55.247000000000014</v>
+      </c>
+      <c r="X12" s="120">
+        <f t="shared" si="9"/>
+        <v>69.035999999999987</v>
+      </c>
+      <c r="Y12" s="116">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="X12" s="120">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="120">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="122">
+      <c r="C13" s="118">
         <v>-4.3031750000000004</v>
       </c>
-      <c r="D13" s="122">
+      <c r="D13" s="118">
         <v>-5.2692839999999999</v>
       </c>
-      <c r="E13" s="122">
+      <c r="E13" s="118">
         <v>-8.6007160000000002</v>
       </c>
-      <c r="F13" s="122">
+      <c r="F13" s="118">
         <v>-15.96838</v>
       </c>
-      <c r="G13" s="123">
+      <c r="G13" s="158">
         <v>-13.761645</v>
       </c>
-      <c r="H13" s="39"/>
+      <c r="H13" s="169">
+        <v>-14.021000000000001</v>
+      </c>
       <c r="L13" s="17">
         <v>-3.3770470000000001</v>
       </c>
-      <c r="M13" s="122">
+      <c r="M13" s="118">
         <v>-3.933446</v>
       </c>
-      <c r="N13" s="122">
+      <c r="N13" s="118">
         <v>-4.1432580000000003</v>
       </c>
-      <c r="O13" s="122">
+      <c r="O13" s="118">
         <f>F13-N13-M13-L13</f>
         <v>-4.5146290000000002</v>
       </c>
-      <c r="P13" s="122">
+      <c r="P13" s="118">
         <v>-4.081442</v>
       </c>
-      <c r="Q13" s="122">
+      <c r="Q13" s="118">
         <v>-2.911133</v>
       </c>
-      <c r="R13" s="122">
+      <c r="R13" s="118">
         <v>-3.327998</v>
       </c>
-      <c r="S13" s="122">
-        <f t="shared" ref="S13:S15" si="9">G13-R13-Q13-P13</f>
+      <c r="S13" s="118">
+        <f t="shared" ref="S13:S15" si="10">G13-R13-Q13-P13</f>
         <v>-3.441072000000001</v>
       </c>
-      <c r="T13" s="122">
+      <c r="T13" s="118">
         <v>-2.9140000000000001</v>
       </c>
-      <c r="U13" s="122">
+      <c r="U13" s="118">
         <v>-3.5009999999999999</v>
       </c>
-      <c r="V13" s="123">
+      <c r="V13" s="158">
         <v>-3.923</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W13" s="175">
+        <f t="shared" ref="W13:W14" si="11">H13-V13-U13-T13</f>
+        <v>-3.6830000000000012</v>
+      </c>
+      <c r="X13" s="119">
+        <v>-3.0150000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>161</v>
       </c>
-      <c r="C14" s="122">
+      <c r="C14" s="118">
         <v>-0.12629099999999999</v>
       </c>
-      <c r="D14" s="122">
+      <c r="D14" s="118">
         <v>-6.5144999999999995E-2</v>
       </c>
-      <c r="E14" s="122">
+      <c r="E14" s="118">
         <v>-0.225606</v>
       </c>
-      <c r="F14" s="122">
+      <c r="F14" s="118">
         <v>1.9334499999999999</v>
       </c>
-      <c r="G14" s="123">
+      <c r="G14" s="158">
         <v>0.354487</v>
       </c>
-      <c r="H14" s="39"/>
+      <c r="H14" s="169">
+        <v>0.123</v>
+      </c>
       <c r="L14" s="17">
         <v>0.113487</v>
       </c>
-      <c r="M14" s="122">
+      <c r="M14" s="118">
         <v>1.0787530000000001</v>
       </c>
-      <c r="N14" s="122">
+      <c r="N14" s="118">
         <v>1.456E-2</v>
       </c>
-      <c r="O14" s="122">
+      <c r="O14" s="118">
         <f>F14-N14-M14-L14</f>
         <v>0.72664999999999991</v>
       </c>
-      <c r="P14" s="122">
+      <c r="P14" s="118">
         <v>-9.1560000000000002E-2</v>
       </c>
-      <c r="Q14" s="122">
+      <c r="Q14" s="118">
         <v>5.0126999999999998E-2</v>
       </c>
-      <c r="R14" s="122">
+      <c r="R14" s="118">
         <v>9.6057000000000003E-2</v>
       </c>
-      <c r="S14" s="122">
-        <f t="shared" si="9"/>
+      <c r="S14" s="118">
+        <f t="shared" si="10"/>
         <v>0.29986299999999999</v>
       </c>
-      <c r="T14" s="122">
+      <c r="T14" s="118">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="U14" s="122">
+      <c r="U14" s="118">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="V14" s="123">
+      <c r="V14" s="158">
         <v>-6.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W14" s="175">
+        <f t="shared" si="11"/>
+        <v>1.7000000000000008E-2</v>
+      </c>
+      <c r="X14" s="119">
+        <v>-3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>162</v>
       </c>
-      <c r="C15" s="122">
+      <c r="C15" s="118">
         <v>0</v>
       </c>
-      <c r="D15" s="122">
+      <c r="D15" s="118">
         <v>-1.092679</v>
       </c>
-      <c r="E15" s="122">
+      <c r="E15" s="118">
         <f>-0.813806+0.050424</f>
         <v>-0.76338200000000001</v>
       </c>
-      <c r="F15" s="122">
+      <c r="F15" s="118">
         <v>-0.45596199999999998</v>
       </c>
-      <c r="G15" s="123">
+      <c r="G15" s="158">
         <f>-1.261556-0.259706</f>
         <v>-1.5212619999999999</v>
       </c>
-      <c r="H15" s="39"/>
+      <c r="H15" s="169"/>
       <c r="L15" s="17">
         <v>-0.42020099999999999</v>
       </c>
-      <c r="M15" s="122">
+      <c r="M15" s="118">
         <v>0.25170599999999999</v>
       </c>
-      <c r="N15" s="122">
+      <c r="N15" s="118">
         <v>8.9227000000000001E-2</v>
       </c>
-      <c r="O15" s="122">
+      <c r="O15" s="118">
         <f>F15-N15-M15-L15</f>
         <v>-0.37669399999999992</v>
       </c>
-      <c r="P15" s="122">
+      <c r="P15" s="118">
         <v>-1.2615559999999999</v>
       </c>
-      <c r="Q15" s="122">
+      <c r="Q15" s="118">
         <v>-0.25970599999999999</v>
       </c>
-      <c r="R15" s="122">
+      <c r="R15" s="118">
         <v>0</v>
       </c>
-      <c r="S15" s="122">
-        <f t="shared" si="9"/>
+      <c r="S15" s="118">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="T15" s="122"/>
-      <c r="U15" s="122"/>
-      <c r="V15" s="123"/>
-    </row>
-    <row r="16" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T15" s="118"/>
+      <c r="U15" s="118"/>
+      <c r="V15" s="158"/>
+      <c r="X15" s="119"/>
+    </row>
+    <row r="16" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C16" s="120">
+      <c r="C16" s="116">
         <f>C12+SUM(C13:C15)</f>
         <v>-32.351775999999994</v>
       </c>
-      <c r="D16" s="120">
-        <f t="shared" ref="D16:I16" si="10">D12+SUM(D13:D15)</f>
+      <c r="D16" s="116">
+        <f t="shared" ref="D16:I16" si="12">D12+SUM(D13:D15)</f>
         <v>-75.109947000000005</v>
       </c>
-      <c r="E16" s="120">
-        <f t="shared" si="10"/>
+      <c r="E16" s="116">
+        <f t="shared" si="12"/>
         <v>-38.024308999999988</v>
       </c>
-      <c r="F16" s="120">
-        <f t="shared" si="10"/>
+      <c r="F16" s="116">
+        <f t="shared" si="12"/>
         <v>7.7095090000000006</v>
       </c>
-      <c r="G16" s="124">
-        <f t="shared" si="10"/>
+      <c r="G16" s="159">
+        <f t="shared" si="12"/>
         <v>67.317145999999966</v>
       </c>
-      <c r="H16" s="10">
-        <f t="shared" si="10"/>
-        <v>449.16</v>
+      <c r="H16" s="13">
+        <f t="shared" si="12"/>
+        <v>162.89099999999999</v>
       </c>
       <c r="I16" s="10">
-        <f t="shared" si="10"/>
-        <v>566.01</v>
+        <f t="shared" si="12"/>
+        <v>573</v>
       </c>
       <c r="L16" s="2">
-        <f t="shared" ref="L16" si="11">L12+SUM(L13:L15)</f>
+        <f t="shared" ref="L16" si="13">L12+SUM(L13:L15)</f>
         <v>1.7361700000000018</v>
       </c>
-      <c r="M16" s="120">
+      <c r="M16" s="116">
         <f>M12+SUM(M13:M15)</f>
         <v>1.1603040000000022</v>
       </c>
-      <c r="N16" s="120">
-        <f t="shared" ref="N16" si="12">N12+SUM(N13:N15)</f>
+      <c r="N16" s="116">
+        <f t="shared" ref="N16" si="14">N12+SUM(N13:N15)</f>
         <v>1.3102739999999988</v>
       </c>
-      <c r="O16" s="120">
-        <f t="shared" ref="O16" si="13">O12+SUM(O13:O15)</f>
+      <c r="O16" s="116">
+        <f t="shared" ref="O16" si="15">O12+SUM(O13:O15)</f>
         <v>3.5027610000000067</v>
       </c>
-      <c r="P16" s="120">
-        <f t="shared" ref="P16" si="14">P12+SUM(P13:P15)</f>
+      <c r="P16" s="116">
+        <f t="shared" ref="P16" si="16">P12+SUM(P13:P15)</f>
         <v>8.4000990000000009</v>
       </c>
-      <c r="Q16" s="120">
-        <f t="shared" ref="Q16:R16" si="15">Q12+SUM(Q13:Q15)</f>
+      <c r="Q16" s="116">
+        <f t="shared" ref="Q16:R16" si="17">Q12+SUM(Q13:Q15)</f>
         <v>13.578667999999997</v>
       </c>
-      <c r="R16" s="120">
-        <f t="shared" si="15"/>
+      <c r="R16" s="116">
+        <f t="shared" si="17"/>
         <v>17.609230000000004</v>
       </c>
-      <c r="S16" s="120">
-        <f t="shared" ref="S16:Y16" si="16">S12+SUM(S13:S15)</f>
+      <c r="S16" s="116">
+        <f t="shared" ref="S16:Y16" si="18">S12+SUM(S13:S15)</f>
         <v>27.729148999999968</v>
       </c>
-      <c r="T16" s="120">
-        <f t="shared" si="16"/>
+      <c r="T16" s="116">
+        <f t="shared" si="18"/>
         <v>47.005999999999993</v>
       </c>
-      <c r="U16" s="120">
+      <c r="U16" s="116">
         <f>U12+SUM(U13:U15)</f>
         <v>32.671999999999997</v>
       </c>
-      <c r="V16" s="124">
-        <f t="shared" si="16"/>
+      <c r="V16" s="159">
+        <f t="shared" si="18"/>
         <v>31.632000000000009</v>
       </c>
-      <c r="W16" s="120">
-        <f t="shared" si="16"/>
+      <c r="W16" s="116">
+        <f t="shared" si="18"/>
+        <v>51.58100000000001</v>
+      </c>
+      <c r="X16" s="120">
+        <f t="shared" si="18"/>
+        <v>65.98899999999999</v>
+      </c>
+      <c r="Y16" s="116">
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="X16" s="120">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="120">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="122">
+      <c r="C17" s="118">
         <v>3.0963999999999998E-2</v>
       </c>
-      <c r="D17" s="122">
+      <c r="D17" s="118">
         <v>5.8416000000000003E-2</v>
       </c>
-      <c r="E17" s="122">
+      <c r="E17" s="118">
         <v>6.9446999999999995E-2</v>
       </c>
-      <c r="F17" s="122">
+      <c r="F17" s="118">
         <v>0.611487</v>
       </c>
-      <c r="G17" s="123">
+      <c r="G17" s="158">
         <v>-11.205164999999999</v>
       </c>
-      <c r="H17" s="39"/>
+      <c r="H17" s="169">
+        <v>29.760999999999999</v>
+      </c>
       <c r="L17" s="17">
         <v>1.1624000000000001E-2</v>
       </c>
-      <c r="M17" s="122">
+      <c r="M17" s="118">
         <v>2.0525999999999999E-2</v>
       </c>
-      <c r="N17" s="122">
+      <c r="N17" s="118">
         <v>1.5873999999999999E-2</v>
       </c>
-      <c r="O17" s="122">
+      <c r="O17" s="118">
         <f>F17-N17-M17-L17</f>
         <v>0.56346299999999994</v>
       </c>
-      <c r="P17" s="122">
+      <c r="P17" s="118">
         <v>0.393094</v>
       </c>
-      <c r="Q17" s="122">
+      <c r="Q17" s="118">
         <v>-16.123213</v>
       </c>
-      <c r="R17" s="122">
+      <c r="R17" s="118">
         <v>2.1629890000000001</v>
       </c>
-      <c r="S17" s="122">
-        <f t="shared" ref="S17:S18" si="17">G17-R17-Q17-P17</f>
+      <c r="S17" s="118">
+        <f t="shared" ref="S17:S18" si="19">G17-R17-Q17-P17</f>
         <v>2.361965000000001</v>
       </c>
-      <c r="T17" s="122">
+      <c r="T17" s="118">
         <v>10.842000000000001</v>
       </c>
-      <c r="U17" s="122">
+      <c r="U17" s="118">
         <v>5.0679999999999996</v>
       </c>
-      <c r="V17" s="123">
+      <c r="V17" s="158">
         <v>4.9610000000000003</v>
       </c>
-    </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="W17" s="175">
+        <f t="shared" ref="W17:W18" si="20">H17-V17-U17-T17</f>
+        <v>8.8899999999999988</v>
+      </c>
+      <c r="X17" s="119">
+        <v>14.686</v>
+      </c>
+    </row>
+    <row r="18" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>163</v>
       </c>
-      <c r="C18" s="122">
+      <c r="C18" s="118">
         <v>0.49450499999999997</v>
       </c>
-      <c r="D18" s="122">
+      <c r="D18" s="118">
         <v>6.9405999999999995E-2</v>
       </c>
-      <c r="E18" s="122">
+      <c r="E18" s="118">
         <v>-1.2078850000000001</v>
       </c>
-      <c r="F18" s="122">
+      <c r="F18" s="118">
         <v>-3.0249999999999999E-3</v>
       </c>
-      <c r="G18" s="123">
+      <c r="G18" s="158">
         <v>0.94079400000000002</v>
       </c>
-      <c r="H18" s="39"/>
+      <c r="H18" s="169">
+        <v>0.90500000000000003</v>
+      </c>
       <c r="L18" s="17">
         <v>0.14580799999999999</v>
       </c>
-      <c r="M18" s="122">
+      <c r="M18" s="118">
         <v>-0.30468699999999999</v>
       </c>
-      <c r="N18" s="122">
+      <c r="N18" s="118">
         <v>0.35846499999999998</v>
       </c>
-      <c r="O18" s="122">
+      <c r="O18" s="118">
         <f>F18-N18-M18-L18</f>
         <v>-0.20261099999999999</v>
       </c>
-      <c r="P18" s="122">
+      <c r="P18" s="118">
         <v>-1.451E-3</v>
       </c>
-      <c r="Q18" s="122">
+      <c r="Q18" s="118">
         <v>-7.5401999999999997E-2</v>
       </c>
-      <c r="R18" s="122">
+      <c r="R18" s="118">
         <v>-7.1597999999999995E-2</v>
       </c>
-      <c r="S18" s="122">
-        <f t="shared" si="17"/>
+      <c r="S18" s="118">
+        <f t="shared" si="19"/>
         <v>1.089245</v>
       </c>
-      <c r="T18" s="122">
+      <c r="T18" s="118">
         <v>-9.2999999999999999E-2</v>
       </c>
-      <c r="U18" s="122">
+      <c r="U18" s="118">
         <v>0.72899999999999998</v>
       </c>
-      <c r="V18" s="123">
+      <c r="V18" s="158">
         <v>0.33900000000000002</v>
       </c>
-    </row>
-    <row r="19" spans="2:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="W18" s="175">
+        <f t="shared" si="20"/>
+        <v>-6.9999999999999923E-2</v>
+      </c>
+      <c r="X18" s="119">
+        <v>7.7999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="120">
-        <f t="shared" ref="C19:F19" si="18">C16-SUM(C17:C18)</f>
+      <c r="C19" s="116">
+        <f t="shared" ref="C19:F19" si="21">C16-SUM(C17:C18)</f>
         <v>-32.877244999999995</v>
       </c>
-      <c r="D19" s="120">
-        <f t="shared" si="18"/>
+      <c r="D19" s="116">
+        <f t="shared" si="21"/>
         <v>-75.237769</v>
       </c>
-      <c r="E19" s="120">
-        <f t="shared" si="18"/>
+      <c r="E19" s="116">
+        <f t="shared" si="21"/>
         <v>-36.885870999999987</v>
       </c>
-      <c r="F19" s="120">
-        <f t="shared" si="18"/>
+      <c r="F19" s="116">
+        <f t="shared" si="21"/>
         <v>7.1010470000000003</v>
       </c>
-      <c r="G19" s="124">
+      <c r="G19" s="159">
         <f>G16-SUM(G17:G18)</f>
         <v>77.581516999999963</v>
       </c>
-      <c r="H19" s="51">
+      <c r="H19" s="170">
         <f>H22*H20</f>
-        <v>122.25797999999999</v>
-      </c>
-      <c r="I19" s="51">
+        <v>120.81471999999999</v>
+      </c>
+      <c r="I19" s="47">
         <f>I22*I20</f>
         <v>0</v>
       </c>
       <c r="L19" s="2">
-        <f t="shared" ref="L19:M19" si="19">L16-SUM(L17:L18)</f>
+        <f t="shared" ref="L19:M19" si="22">L16-SUM(L17:L18)</f>
         <v>1.5787380000000018</v>
       </c>
-      <c r="M19" s="120">
-        <f t="shared" si="19"/>
+      <c r="M19" s="116">
+        <f t="shared" si="22"/>
         <v>1.4444650000000023</v>
       </c>
-      <c r="N19" s="120">
-        <f t="shared" ref="N19" si="20">N16-SUM(N17:N18)</f>
+      <c r="N19" s="116">
+        <f t="shared" ref="N19" si="23">N16-SUM(N17:N18)</f>
         <v>0.93593499999999885</v>
       </c>
-      <c r="O19" s="120">
-        <f t="shared" ref="O19" si="21">O16-SUM(O17:O18)</f>
+      <c r="O19" s="116">
+        <f t="shared" ref="O19" si="24">O16-SUM(O17:O18)</f>
         <v>3.1419090000000067</v>
       </c>
-      <c r="P19" s="120">
-        <f t="shared" ref="P19" si="22">P16-SUM(P17:P18)</f>
+      <c r="P19" s="116">
+        <f t="shared" ref="P19" si="25">P16-SUM(P17:P18)</f>
         <v>8.0084560000000007</v>
       </c>
-      <c r="Q19" s="120">
-        <f t="shared" ref="Q19:R19" si="23">Q16-SUM(Q17:Q18)</f>
+      <c r="Q19" s="116">
+        <f t="shared" ref="Q19:R19" si="26">Q16-SUM(Q17:Q18)</f>
         <v>29.777282999999997</v>
       </c>
-      <c r="R19" s="120">
-        <f t="shared" si="23"/>
+      <c r="R19" s="116">
+        <f t="shared" si="26"/>
         <v>15.517839000000004</v>
       </c>
-      <c r="S19" s="120">
-        <f t="shared" ref="S19:Y19" si="24">S16-SUM(S17:S18)</f>
+      <c r="S19" s="116">
+        <f t="shared" ref="S19:Y19" si="27">S16-SUM(S17:S18)</f>
         <v>24.277938999999968</v>
       </c>
-      <c r="T19" s="120">
-        <f t="shared" si="24"/>
+      <c r="T19" s="116">
+        <f t="shared" si="27"/>
         <v>36.256999999999991</v>
       </c>
-      <c r="U19" s="120">
-        <f t="shared" si="24"/>
+      <c r="U19" s="116">
+        <f t="shared" si="27"/>
         <v>26.874999999999996</v>
       </c>
-      <c r="V19" s="124">
-        <f t="shared" si="24"/>
+      <c r="V19" s="159">
+        <f t="shared" si="27"/>
         <v>26.332000000000008</v>
       </c>
-      <c r="W19" s="120">
-        <f t="shared" si="24"/>
+      <c r="W19" s="116">
+        <f t="shared" si="27"/>
+        <v>42.76100000000001</v>
+      </c>
+      <c r="X19" s="120">
+        <f t="shared" si="27"/>
+        <v>51.295199999999994</v>
+      </c>
+      <c r="Y19" s="116">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="X19" s="120">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="120">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>164</v>
       </c>
-      <c r="C20" s="122">
+      <c r="C20" s="118">
         <v>186.842646</v>
       </c>
-      <c r="D20" s="122">
+      <c r="D20" s="118">
         <v>200.34402800000001</v>
       </c>
-      <c r="E20" s="122">
+      <c r="E20" s="118">
         <v>5.4436049999999998</v>
       </c>
-      <c r="F20" s="122">
+      <c r="F20" s="118">
         <v>5.6785269999999999</v>
       </c>
-      <c r="G20" s="123">
+      <c r="G20" s="158">
         <v>5.981795</v>
       </c>
-      <c r="H20" s="122">
-        <f>T20</f>
-        <v>36.170999999999999</v>
+      <c r="H20" s="119">
+        <v>35.744</v>
       </c>
       <c r="L20" s="17">
         <v>5.5568299999999997</v>
       </c>
-      <c r="M20" s="122">
+      <c r="M20" s="118">
         <v>5.6557409999999999</v>
       </c>
-      <c r="N20" s="121">
+      <c r="N20" s="117">
         <v>5.7296649999999998</v>
       </c>
-      <c r="O20" s="122">
+      <c r="O20" s="118">
         <f>F20</f>
         <v>5.6785269999999999</v>
       </c>
-      <c r="P20" s="122">
+      <c r="P20" s="118">
         <v>5.9607679999999998</v>
       </c>
-      <c r="Q20" s="122">
+      <c r="Q20" s="118">
         <v>6.0243779999999996</v>
       </c>
-      <c r="R20" s="122">
+      <c r="R20" s="118">
         <v>5.9058830000000002</v>
       </c>
-      <c r="S20" s="122">
+      <c r="S20" s="118">
         <f>G20</f>
         <v>5.981795</v>
       </c>
-      <c r="T20" s="122">
+      <c r="T20" s="118">
         <v>36.170999999999999</v>
       </c>
-      <c r="U20" s="122">
+      <c r="U20" s="118">
         <v>35.506999999999998</v>
       </c>
-      <c r="V20" s="123">
+      <c r="V20" s="158">
         <v>35.674999999999997</v>
       </c>
-    </row>
-    <row r="21" spans="2:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="W20" s="158">
+        <v>35.674999999999997</v>
+      </c>
+      <c r="X20" s="119">
+        <v>34.932000000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="2:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>17</v>
       </c>
@@ -17676,26 +17862,27 @@
         <f>E19/E20</f>
         <v>-6.77600064663031</v>
       </c>
-      <c r="F21" s="132">
+      <c r="F21" s="127">
         <f>F19/F20</f>
         <v>1.2505086266209531</v>
       </c>
-      <c r="G21" s="50">
+      <c r="G21" s="172">
         <f>G19/G20</f>
         <v>12.969604775823973</v>
       </c>
-      <c r="H21" s="143">
-        <v>3.27</v>
+      <c r="H21" s="46">
+        <f>H19/H20</f>
+        <v>3.38</v>
       </c>
       <c r="I21" s="8">
         <v>4.2699999999999996</v>
       </c>
       <c r="L21" s="2">
-        <f t="shared" ref="L21:M21" si="25">(L19+L18)/L20</f>
+        <f t="shared" ref="L21:M21" si="28">(L19+L18)/L20</f>
         <v>0.3103470863783851</v>
       </c>
       <c r="M21" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0.2015258478066804</v>
       </c>
       <c r="N21" s="2">
@@ -17703,11 +17890,11 @@
         <v>0.22591198612833366</v>
       </c>
       <c r="O21" s="2">
-        <f t="shared" ref="O21:S21" si="26">(O19+O18)/O20</f>
+        <f t="shared" ref="O21:S21" si="29">(O19+O18)/O20</f>
         <v>0.5176162761927533</v>
       </c>
       <c r="P21" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1.3432841204354877</v>
       </c>
       <c r="Q21" s="2">
@@ -17715,39 +17902,39 @@
         <v>4.9302817651880408</v>
       </c>
       <c r="R21" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>2.615399085962252</v>
       </c>
       <c r="S21" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4.2407310849000952</v>
       </c>
       <c r="T21" s="2">
-        <f t="shared" ref="T21:Y21" si="27">(T19+T18)/T20</f>
+        <f t="shared" ref="T21:Y21" si="30">(T19+T18)/T20</f>
         <v>0.99980647480025397</v>
       </c>
       <c r="U21" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.77742416988199503</v>
       </c>
-      <c r="V21" s="34">
-        <f t="shared" si="27"/>
+      <c r="V21" s="164">
+        <f t="shared" si="30"/>
         <v>0.74761037140854969</v>
       </c>
-      <c r="W21" s="8">
-        <f>W22</f>
-        <v>0.98</v>
-      </c>
-      <c r="X21" s="8">
+      <c r="W21" s="164">
+        <f t="shared" si="30"/>
+        <v>1.1966643307638405</v>
+      </c>
+      <c r="X21" s="38">
         <f>X22</f>
         <v>1.22</v>
       </c>
       <c r="Y21" s="2" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="22" spans="2:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
         <v>54</v>
       </c>
@@ -17755,129 +17942,153 @@
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="134">
+      <c r="G22" s="173">
         <v>6.73</v>
       </c>
-      <c r="H22" s="42">
+      <c r="H22" s="171">
         <v>3.38</v>
       </c>
       <c r="I22" s="1">
-        <v>4.38</v>
-      </c>
-      <c r="L22" s="44"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="44"/>
-      <c r="O22" s="43"/>
-      <c r="P22" s="43"/>
-      <c r="Q22" s="43"/>
-      <c r="R22" s="43">
+        <v>4.7</v>
+      </c>
+      <c r="J22" s="1">
+        <v>5.99</v>
+      </c>
+      <c r="L22" s="40"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="39"/>
+      <c r="R22" s="39">
         <v>0.89</v>
       </c>
-      <c r="S22" s="43"/>
-      <c r="T22" s="43"/>
-      <c r="U22" s="137">
+      <c r="S22" s="39"/>
+      <c r="T22" s="39"/>
+      <c r="U22" s="131">
         <v>0.56000000000000005</v>
       </c>
-      <c r="V22" s="138">
+      <c r="V22" s="165">
         <v>0.65</v>
       </c>
       <c r="W22" s="1">
         <v>0.98</v>
       </c>
-      <c r="X22" s="1">
+      <c r="X22" s="15">
         <v>1.22</v>
       </c>
-    </row>
-    <row r="23" spans="2:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Y22" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="Z22" s="1">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AA22" s="1">
+        <v>1.35</v>
+      </c>
+      <c r="AB22" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="AC22" s="1">
+        <v>1.22</v>
+      </c>
+      <c r="AD22" s="1">
+        <v>1.42</v>
+      </c>
+      <c r="AE22" s="1">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="23" spans="2:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="38">
-        <f t="shared" ref="C23:E23" si="28">1-(C6)/C3</f>
+      <c r="C23" s="37">
+        <f t="shared" ref="C23:E23" si="31">1-(C6)/C3</f>
         <v>0.61744707145930278</v>
       </c>
-      <c r="D23" s="38">
-        <f t="shared" si="28"/>
+      <c r="D23" s="37">
+        <f t="shared" si="31"/>
         <v>0.62134282197000457</v>
       </c>
-      <c r="E23" s="38">
-        <f t="shared" si="28"/>
+      <c r="E23" s="37">
+        <f t="shared" si="31"/>
         <v>0.67526732664735967</v>
       </c>
-      <c r="F23" s="38">
+      <c r="F23" s="37">
         <f>1-(F6)/F3</f>
         <v>0.75396233553224834</v>
       </c>
-      <c r="G23" s="5">
-        <f t="shared" ref="G23:I23" si="29">1-(G6)/G3</f>
+      <c r="G23" s="37">
+        <f t="shared" ref="G23:I23" si="32">1-(G6)/G3</f>
         <v>0.81055306777919456</v>
       </c>
-      <c r="H23" s="38">
-        <f t="shared" si="29"/>
+      <c r="H23" s="5">
+        <f t="shared" si="32"/>
+        <v>0.85351082328956052</v>
+      </c>
+      <c r="I23" s="37">
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="I23" s="38">
-        <f t="shared" si="29"/>
-        <v>1</v>
-      </c>
-      <c r="L23" s="38">
-        <f t="shared" ref="L23:S23" si="30">1-(L6)/L3</f>
+      <c r="L23" s="37">
+        <f t="shared" ref="L23:S23" si="33">1-(L6)/L3</f>
         <v>0.76239484347539765</v>
       </c>
-      <c r="M23" s="38">
-        <f t="shared" si="30"/>
+      <c r="M23" s="37">
+        <f t="shared" si="33"/>
         <v>0.77256785764017144</v>
       </c>
-      <c r="N23" s="38">
-        <f t="shared" si="30"/>
+      <c r="N23" s="37">
+        <f t="shared" si="33"/>
         <v>0.75671444766418616</v>
       </c>
-      <c r="O23" s="38">
-        <f t="shared" si="30"/>
+      <c r="O23" s="37">
+        <f t="shared" si="33"/>
         <v>0.73239191660374248</v>
       </c>
-      <c r="P23" s="38">
-        <f t="shared" si="30"/>
+      <c r="P23" s="37">
+        <f t="shared" si="33"/>
         <v>0.74909559950167992</v>
       </c>
-      <c r="Q23" s="38">
+      <c r="Q23" s="37">
         <f>1-(Q6)/Q3</f>
         <v>0.80807745356071237</v>
       </c>
-      <c r="R23" s="38">
-        <f t="shared" si="30"/>
+      <c r="R23" s="37">
+        <f t="shared" si="33"/>
         <v>0.81758348771116529</v>
       </c>
-      <c r="S23" s="38">
-        <f t="shared" si="30"/>
+      <c r="S23" s="37">
+        <f t="shared" si="33"/>
         <v>0.83635059832181968</v>
       </c>
-      <c r="T23" s="38">
-        <f t="shared" ref="T23:U23" si="31">1-(T6)/T3</f>
+      <c r="T23" s="37">
+        <f t="shared" ref="T23:U23" si="34">1-(T6)/T3</f>
         <v>0.85400144883330786</v>
       </c>
-      <c r="U23" s="38">
-        <f t="shared" si="31"/>
+      <c r="U23" s="37">
+        <f t="shared" si="34"/>
         <v>0.85569694636380211</v>
       </c>
-      <c r="V23" s="5">
-        <f t="shared" ref="V23:Y23" si="32">1-(V6)/V3</f>
+      <c r="V23" s="37">
+        <f t="shared" ref="V23:Y23" si="35">1-(V6)/V3</f>
         <v>0.8507226274872427</v>
       </c>
-      <c r="W23" s="38" t="e">
-        <f t="shared" si="32"/>
+      <c r="W23" s="37">
+        <f t="shared" si="35"/>
+        <v>0.85396052945660639</v>
+      </c>
+      <c r="X23" s="5">
+        <f t="shared" si="35"/>
+        <v>0.86336036122444459</v>
+      </c>
+      <c r="Y23" s="37" t="e">
+        <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X23" s="38" t="e">
-        <f t="shared" si="32"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y23" s="38" t="e">
-        <f t="shared" si="32"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>24</v>
       </c>
@@ -17897,40 +18108,40 @@
         <f>F19/F3</f>
         <v>4.4560685503845419E-2</v>
       </c>
-      <c r="G24" s="6">
-        <f t="shared" ref="G24:I24" si="33">G19/G3</f>
+      <c r="G24" s="161">
+        <f t="shared" ref="G24:I24" si="36">G19/G3</f>
         <v>0.28614362395546977</v>
       </c>
-      <c r="H24" s="3">
-        <f t="shared" si="33"/>
-        <v>0.27219249265295214</v>
+      <c r="H24" s="6">
+        <f t="shared" si="36"/>
+        <v>0.26831080285778369</v>
       </c>
       <c r="I24" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <f t="shared" ref="L24:Q24" si="34">L19/L3</f>
+        <f t="shared" ref="L24:Q24" si="37">L19/L3</f>
         <v>4.5531634870515168E-2</v>
       </c>
       <c r="M24" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>4.1344062346467696E-2</v>
       </c>
       <c r="N24" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>2.2914758450042857E-2</v>
       </c>
       <c r="O24" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>6.4249779786806169E-2</v>
       </c>
       <c r="P24" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>0.17047017586760826</v>
       </c>
       <c r="Q24" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>0.53203641941123847</v>
       </c>
       <c r="R24" s="3">
@@ -17946,103 +18157,106 @@
         <v>0.34559440292816829</v>
       </c>
       <c r="U24" s="3">
-        <f t="shared" ref="U24" si="35">U19/U4</f>
+        <f t="shared" ref="U24" si="38">U19/U4</f>
         <v>0.28795671273974066</v>
       </c>
-      <c r="V24" s="6">
-        <f t="shared" ref="V24:Y24" si="36">V19/V4</f>
+      <c r="V24" s="161">
+        <f t="shared" ref="V24:Y24" si="39">V19/V4</f>
         <v>0.25149952244508123</v>
       </c>
       <c r="W24" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
+        <v>0.33171204716468861</v>
+      </c>
+      <c r="X24" s="6">
+        <f>X19/X4</f>
+        <v>0.40043091334894609</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="X24" s="3">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3" t="e">
-        <f t="shared" si="36"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="25" spans="2:25" s="125" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="125" t="s">
+    </row>
+    <row r="25" spans="2:31" s="121" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="121" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="142"/>
-      <c r="D25" s="126">
+      <c r="C25" s="135"/>
+      <c r="D25" s="122">
         <f>D3/C3-1</f>
         <v>0.95305337511785693</v>
       </c>
-      <c r="E25" s="127">
+      <c r="E25" s="123">
         <f>E3/D3-1</f>
         <v>9.3660696466152382E-2</v>
       </c>
-      <c r="F25" s="127">
+      <c r="F25" s="123">
         <f>F3/E3-1</f>
         <v>0.26906277250392074</v>
       </c>
-      <c r="G25" s="128">
-        <f t="shared" ref="G25:I25" si="37">G3/F3-1</f>
+      <c r="G25" s="123">
+        <f t="shared" ref="G25:J25" si="40">G3/F3-1</f>
         <v>0.70138919480622985</v>
       </c>
-      <c r="H25" s="127">
-        <f t="shared" si="37"/>
-        <v>0.65663517685325568</v>
-      </c>
-      <c r="I25" s="127">
-        <f t="shared" si="37"/>
-        <v>0.2601522842639592</v>
-      </c>
-      <c r="J25"/>
+      <c r="H25" s="124">
+        <f t="shared" si="40"/>
+        <v>0.66076238043972535</v>
+      </c>
+      <c r="I25" s="123">
+        <f t="shared" si="40"/>
+        <v>0.27254435583271697</v>
+      </c>
+      <c r="J25" s="123">
+        <f>J4/I4-1</f>
+        <v>0.2443280977312392</v>
+      </c>
       <c r="K25"/>
-      <c r="L25" s="145"/>
-      <c r="M25" s="145"/>
-      <c r="N25" s="145"/>
-      <c r="O25" s="145"/>
-      <c r="P25" s="127">
-        <f t="shared" ref="P25" si="38">P3/L3-1</f>
+      <c r="L25" s="136"/>
+      <c r="M25" s="136"/>
+      <c r="N25" s="136"/>
+      <c r="O25" s="136"/>
+      <c r="P25" s="123">
+        <f t="shared" ref="P25" si="41">P3/L3-1</f>
         <v>0.3548885312214991</v>
       </c>
-      <c r="Q25" s="127">
-        <f t="shared" ref="Q25:V25" si="39">Q3/M3-1</f>
+      <c r="Q25" s="123">
+        <f t="shared" ref="Q25:V25" si="42">Q3/M3-1</f>
         <v>0.60195322154471387</v>
       </c>
-      <c r="R25" s="127">
-        <f t="shared" si="39"/>
+      <c r="R25" s="123">
+        <f t="shared" si="42"/>
         <v>0.71279372070468461</v>
       </c>
-      <c r="S25" s="127">
-        <f t="shared" si="39"/>
+      <c r="S25" s="123">
+        <f t="shared" si="42"/>
         <v>1.0085909474100725</v>
       </c>
-      <c r="T25" s="127">
-        <f t="shared" si="39"/>
+      <c r="T25" s="123">
+        <f t="shared" si="42"/>
         <v>1.2331854093501313</v>
       </c>
-      <c r="U25" s="127">
-        <f t="shared" si="39"/>
+      <c r="U25" s="123">
+        <f t="shared" si="42"/>
         <v>0.76352754106974974</v>
       </c>
-      <c r="V25" s="128">
-        <f t="shared" si="39"/>
+      <c r="V25" s="123">
+        <f t="shared" si="42"/>
         <v>0.66952336948913893</v>
       </c>
-      <c r="W25" s="127">
+      <c r="W25" s="123">
         <f>W4/S3-1</f>
         <v>0.31242093251829073</v>
       </c>
-      <c r="X25" s="127">
-        <f t="shared" ref="X25:Y25" si="40">X4/T3-1</f>
+      <c r="X25" s="124">
+        <f>X4/T3-1</f>
         <v>0.22102333384169581</v>
       </c>
-      <c r="Y25" s="127">
-        <f t="shared" si="40"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Y25" s="123">
+        <f t="shared" ref="X25:Y25" si="43">Y4/U3-1</f>
+        <v>0.33735891876557722</v>
+      </c>
+    </row>
+    <row r="26" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>56</v>
       </c>
@@ -18062,76 +18276,80 @@
         <f>F8/F3</f>
         <v>7.5202445742312093E-2</v>
       </c>
-      <c r="G26" s="6">
-        <f t="shared" ref="G26:I26" si="41">G8/G3</f>
+      <c r="G26" s="161">
+        <f t="shared" ref="G26:J26" si="44">G8/G3</f>
         <v>3.5923132068781269E-2</v>
       </c>
-      <c r="H26" s="3">
-        <f t="shared" si="41"/>
+      <c r="H26" s="6">
+        <f t="shared" si="44"/>
+        <v>7.149123099234031E-2</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="I26" s="3">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
-        <f t="shared" ref="L26:S26" si="42">L8/L3</f>
-        <v>9.2265862008291025E-2</v>
-      </c>
-      <c r="M26" s="3">
-        <f t="shared" si="42"/>
-        <v>9.4844976045193624E-2</v>
-      </c>
-      <c r="N26" s="3">
-        <f t="shared" si="42"/>
-        <v>8.8515356194628469E-2</v>
-      </c>
-      <c r="O26" s="3">
-        <f t="shared" si="42"/>
-        <v>3.795067531194099E-2</v>
-      </c>
-      <c r="P26" s="3">
-        <f t="shared" si="42"/>
-        <v>1.3939847633713658E-2</v>
-      </c>
-      <c r="Q26" s="3">
-        <f t="shared" si="42"/>
-        <v>1.7779445779371808E-2</v>
-      </c>
-      <c r="R26" s="3">
-        <f t="shared" si="42"/>
-        <v>3.8960905670828959E-2</v>
-      </c>
-      <c r="S26" s="3">
-        <f t="shared" si="42"/>
-        <v>5.4612267221159694E-2</v>
-      </c>
-      <c r="T26" s="3">
-        <f t="shared" ref="T26:U26" si="43">T8/T3</f>
-        <v>5.0956992527070304E-2</v>
-      </c>
-      <c r="U26" s="3">
-        <f t="shared" si="43"/>
-        <v>8.8873579056148816E-2</v>
-      </c>
-      <c r="V26" s="6">
-        <f t="shared" ref="V26:Y26" si="44">V8/V3</f>
-        <v>7.5130997636905367E-2</v>
-      </c>
-      <c r="W26" s="3" t="e">
+      <c r="J26" s="3" t="e">
         <f t="shared" si="44"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X26" s="3" t="e">
-        <f t="shared" si="44"/>
+      <c r="L26" s="3">
+        <f t="shared" ref="L26:S26" si="45">L8/L3</f>
+        <v>9.2265862008291025E-2</v>
+      </c>
+      <c r="M26" s="3">
+        <f t="shared" si="45"/>
+        <v>9.4844976045193624E-2</v>
+      </c>
+      <c r="N26" s="3">
+        <f t="shared" si="45"/>
+        <v>8.8515356194628469E-2</v>
+      </c>
+      <c r="O26" s="3">
+        <f t="shared" si="45"/>
+        <v>3.795067531194099E-2</v>
+      </c>
+      <c r="P26" s="3">
+        <f t="shared" si="45"/>
+        <v>1.3939847633713658E-2</v>
+      </c>
+      <c r="Q26" s="3">
+        <f t="shared" si="45"/>
+        <v>1.7779445779371808E-2</v>
+      </c>
+      <c r="R26" s="3">
+        <f t="shared" si="45"/>
+        <v>3.8960905670828959E-2</v>
+      </c>
+      <c r="S26" s="3">
+        <f t="shared" si="45"/>
+        <v>5.4612267221159694E-2</v>
+      </c>
+      <c r="T26" s="3">
+        <f t="shared" ref="T26:U26" si="46">T8/T3</f>
+        <v>5.0956992527070304E-2</v>
+      </c>
+      <c r="U26" s="3">
+        <f t="shared" si="46"/>
+        <v>8.8873579056148816E-2</v>
+      </c>
+      <c r="V26" s="161">
+        <f t="shared" ref="V26:Y26" si="47">V8/V3</f>
+        <v>7.5130997636905367E-2</v>
+      </c>
+      <c r="W26" s="3">
+        <f t="shared" si="47"/>
+        <v>7.1595222878439072E-2</v>
+      </c>
+      <c r="X26" s="6">
+        <f>X8/X3</f>
+        <v>8.2972428599886391E-2</v>
+      </c>
+      <c r="Y26" s="3" t="e">
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y26" s="3" t="e">
-        <f t="shared" si="44"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>165</v>
       </c>
@@ -18151,76 +18369,80 @@
         <f>F5/F3</f>
         <v>0.29100686728267811</v>
       </c>
-      <c r="G27" s="6">
-        <f t="shared" ref="G27:I27" si="45">G5/G3</f>
+      <c r="G27" s="161">
+        <f t="shared" ref="G27:J27" si="48">G5/G3</f>
         <v>0.19092452642920654</v>
       </c>
-      <c r="H27" s="3">
-        <f t="shared" si="45"/>
+      <c r="H27" s="6">
+        <f t="shared" si="48"/>
+        <v>0.12175784347038171</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="I27" s="3">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
-        <f t="shared" ref="L27:S27" si="46">L5/L3</f>
-        <v>0.33379996343598073</v>
-      </c>
-      <c r="M27" s="3">
-        <f t="shared" si="46"/>
-        <v>0.34395747397543591</v>
-      </c>
-      <c r="N27" s="3">
-        <f t="shared" si="46"/>
-        <v>0.27125451664484757</v>
-      </c>
-      <c r="O27" s="3">
-        <f t="shared" si="46"/>
-        <v>0.23933184019500423</v>
-      </c>
-      <c r="P27" s="3">
-        <f t="shared" si="46"/>
-        <v>0.23468200458957578</v>
-      </c>
-      <c r="Q27" s="3">
-        <f t="shared" si="46"/>
-        <v>0.22756589621252166</v>
-      </c>
-      <c r="R27" s="3">
-        <f t="shared" si="46"/>
-        <v>0.19188344852605271</v>
-      </c>
-      <c r="S27" s="3">
-        <f t="shared" si="46"/>
-        <v>0.14843436968874724</v>
-      </c>
-      <c r="T27" s="3">
-        <f t="shared" ref="T27:U27" si="47">T5/T3</f>
-        <v>0.14343449748360529</v>
-      </c>
-      <c r="U27" s="3">
-        <f t="shared" si="47"/>
-        <v>0.11834613280379323</v>
-      </c>
-      <c r="V27" s="6">
-        <f t="shared" ref="V27:Y27" si="48">V5/V3</f>
-        <v>0.12260693859378745</v>
-      </c>
-      <c r="W27" s="3" t="e">
+      <c r="J27" s="3" t="e">
         <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X27" s="3" t="e">
-        <f t="shared" si="48"/>
+      <c r="L27" s="3">
+        <f t="shared" ref="L27:S27" si="49">L5/L3</f>
+        <v>0.33379996343598073</v>
+      </c>
+      <c r="M27" s="3">
+        <f t="shared" si="49"/>
+        <v>0.34395747397543591</v>
+      </c>
+      <c r="N27" s="3">
+        <f t="shared" si="49"/>
+        <v>0.27125451664484757</v>
+      </c>
+      <c r="O27" s="3">
+        <f t="shared" si="49"/>
+        <v>0.23933184019500423</v>
+      </c>
+      <c r="P27" s="3">
+        <f t="shared" si="49"/>
+        <v>0.23468200458957578</v>
+      </c>
+      <c r="Q27" s="3">
+        <f t="shared" si="49"/>
+        <v>0.22756589621252166</v>
+      </c>
+      <c r="R27" s="3">
+        <f t="shared" si="49"/>
+        <v>0.19188344852605271</v>
+      </c>
+      <c r="S27" s="3">
+        <f t="shared" si="49"/>
+        <v>0.14843436968874724</v>
+      </c>
+      <c r="T27" s="3">
+        <f t="shared" ref="T27:U27" si="50">T5/T3</f>
+        <v>0.14343449748360529</v>
+      </c>
+      <c r="U27" s="3">
+        <f t="shared" si="50"/>
+        <v>0.11834613280379323</v>
+      </c>
+      <c r="V27" s="161">
+        <f t="shared" ref="V27:Y27" si="51">V5/V3</f>
+        <v>0.12260693859378745</v>
+      </c>
+      <c r="W27" s="3">
+        <f t="shared" si="51"/>
+        <v>0.10607612286226895</v>
+      </c>
+      <c r="X27" s="6">
+        <f>X5/X3</f>
+        <v>0.10821239643202327</v>
+      </c>
+      <c r="Y27" s="3" t="e">
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y27" s="3" t="e">
-        <f t="shared" si="48"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>123</v>
       </c>
@@ -18236,337 +18458,344 @@
         <f>E11/E3</f>
         <v>-8.7600233879882611E-2</v>
       </c>
-      <c r="F28" s="3">
-        <f>F11/F3</f>
+      <c r="F28" s="161">
+        <f>F9/F3</f>
+        <v>5.3890279604810264E-2</v>
+      </c>
+      <c r="G28" s="161">
+        <f>G9/G3</f>
+        <v>4.2059369104373592E-2</v>
+      </c>
+      <c r="H28" s="161">
+        <f>H9/H3</f>
+        <v>3.7252459030956364E-2</v>
+      </c>
+      <c r="I28" s="161">
+        <f>I9/I3</f>
         <v>0</v>
       </c>
-      <c r="G28" s="6">
-        <f t="shared" ref="G28:I28" si="49">G11/G3</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="3">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="3">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="3">
-        <f t="shared" ref="L28:S28" si="50">L11/L3</f>
-        <v>0</v>
-      </c>
-      <c r="M28" s="3">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="N28" s="3">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="O28" s="3">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="P28" s="3">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="3">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="R28" s="3">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="S28" s="3">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="T28" s="3">
-        <f t="shared" ref="T28:U28" si="51">T11/T3</f>
-        <v>0</v>
-      </c>
-      <c r="U28" s="3">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="V28" s="6">
-        <f t="shared" ref="V28:Y28" si="52">V11/V3</f>
-        <v>0</v>
-      </c>
-      <c r="W28" s="3" t="e">
+      <c r="J28" s="161" t="e">
+        <f>J9/J3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L28" s="161">
+        <f t="shared" ref="L28:V28" si="52">L9/L3</f>
+        <v>8.0701849205519927E-2</v>
+      </c>
+      <c r="M28" s="161">
         <f t="shared" si="52"/>
+        <v>4.8590224904841231E-2</v>
+      </c>
+      <c r="N28" s="161">
+        <f t="shared" si="52"/>
+        <v>5.3473343743460675E-2</v>
+      </c>
+      <c r="O28" s="161">
+        <f t="shared" si="52"/>
+        <v>3.9014487804304464E-2</v>
+      </c>
+      <c r="P28" s="161">
+        <f t="shared" si="52"/>
+        <v>5.0656602744132577E-2</v>
+      </c>
+      <c r="Q28" s="161">
+        <f t="shared" si="52"/>
+        <v>4.5057162059268865E-2</v>
+      </c>
+      <c r="R28" s="161">
+        <f t="shared" si="52"/>
+        <v>3.454875318855221E-2</v>
+      </c>
+      <c r="S28" s="161">
+        <f t="shared" si="52"/>
+        <v>4.1588574006959263E-2</v>
+      </c>
+      <c r="T28" s="161">
+        <f t="shared" si="52"/>
+        <v>2.9844059783437543E-2</v>
+      </c>
+      <c r="U28" s="161">
+        <f t="shared" si="52"/>
+        <v>3.8965775769487954E-2</v>
+      </c>
+      <c r="V28" s="161">
+        <f t="shared" si="52"/>
+        <v>4.1294222404876881E-2</v>
+      </c>
+      <c r="W28" s="161">
+        <f>W9/W3</f>
+        <v>3.8300133211158938E-2</v>
+      </c>
+      <c r="X28" s="6">
+        <f>X9/X3</f>
+        <v>2.9364242026280261E-2</v>
+      </c>
+      <c r="Y28" s="3" t="e">
+        <f t="shared" ref="V28:Y28" si="53">Y11/Y3</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X28" s="3" t="e">
-        <f t="shared" si="52"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y28" s="3" t="e">
-        <f t="shared" si="52"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="29" spans="2:25" s="125" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="125" t="s">
+    </row>
+    <row r="29" spans="2:31" s="121" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="121" t="s">
         <v>168</v>
       </c>
-      <c r="C29" s="126"/>
-      <c r="D29" s="126">
+      <c r="C29" s="122"/>
+      <c r="D29" s="122">
         <f>-(D19/C19-1)</f>
         <v>-1.2884450628390551</v>
       </c>
-      <c r="E29" s="127">
+      <c r="E29" s="123">
         <f>E19/D19-1</f>
         <v>-0.50974262673844062</v>
       </c>
-      <c r="F29" s="127">
+      <c r="F29" s="123">
         <f>F21/E21-1</f>
         <v>-1.1845496616419049</v>
       </c>
-      <c r="G29" s="128">
-        <f t="shared" ref="G29" si="53">G21/F21-1</f>
+      <c r="G29" s="123">
+        <f t="shared" ref="G29" si="54">G21/F21-1</f>
         <v>9.3714636586471496</v>
       </c>
-      <c r="H29" s="127">
+      <c r="H29" s="124">
         <f>H22/(G21*G20/H20)-1</f>
-        <v>0.57586477717366691</v>
-      </c>
-      <c r="I29" s="127">
+        <v>0.55726163488141212</v>
+      </c>
+      <c r="I29" s="123">
         <f>I22/(H22)-1</f>
-        <v>0.29585798816568043</v>
-      </c>
-      <c r="J29"/>
+        <v>0.39053254437869822</v>
+      </c>
+      <c r="J29" s="123">
+        <f>J22/(I22)-1</f>
+        <v>0.27446808510638299</v>
+      </c>
       <c r="K29"/>
-      <c r="L29" s="145"/>
-      <c r="M29" s="145"/>
-      <c r="N29" s="145"/>
-      <c r="O29" s="145"/>
-      <c r="P29" s="127">
-        <f t="shared" ref="P29" si="54">P21/L21-1</f>
+      <c r="L29" s="136"/>
+      <c r="M29" s="136"/>
+      <c r="N29" s="136"/>
+      <c r="O29" s="136"/>
+      <c r="P29" s="123">
+        <f t="shared" ref="P29" si="55">P21/L21-1</f>
         <v>3.3283284406211981</v>
       </c>
-      <c r="Q29" s="127">
+      <c r="Q29" s="123">
         <f>Q21/M21-1</f>
         <v>23.46476131398072</v>
       </c>
-      <c r="R29" s="127">
+      <c r="R29" s="123">
         <f>R21/N21-1</f>
         <v>10.577070923879727</v>
       </c>
-      <c r="S29" s="127">
+      <c r="S29" s="123">
         <f>S21/O21-1</f>
         <v>7.1928086112209204</v>
       </c>
-      <c r="T29" s="127">
+      <c r="T29" s="123">
         <f>T21/(P21*P20/T20)-1</f>
         <v>3.5165452001091522</v>
       </c>
-      <c r="U29" s="127">
+      <c r="U29" s="123">
         <f>U21/(Q21*Q20/U20)-1</f>
         <v>-7.0631250593186423E-2</v>
       </c>
-      <c r="V29" s="128">
-        <f t="shared" ref="V29:Y29" si="55">V22/(R21*R20/U20)-1</f>
+      <c r="V29" s="123">
+        <f t="shared" ref="V29:Y29" si="56">V22/(R21*R20/U20)-1</f>
         <v>0.49418554326583353</v>
       </c>
-      <c r="W29" s="127">
+      <c r="W29" s="123">
         <f>W22/(S21*S20/V20)-1</f>
         <v>0.37821762163273775</v>
       </c>
-      <c r="X29" s="127">
+      <c r="X29" s="124">
         <f>X22/(T21*T20/V20)-1</f>
         <v>0.20350348412786223</v>
       </c>
-      <c r="Y29" s="127" t="e">
-        <f t="shared" si="55"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Y29" s="123">
+        <f t="shared" si="56"/>
+        <v>0.25281408491523005</v>
+      </c>
+    </row>
+    <row r="30" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="46">
+      <c r="C30" s="42">
         <f>C13/C3</f>
         <v>-7.3197846788253168E-2</v>
       </c>
-      <c r="D30" s="46">
+      <c r="D30" s="42">
         <f>D13/D3</f>
         <v>-4.5893036318300044E-2</v>
       </c>
-      <c r="E30" s="46">
+      <c r="E30" s="42">
         <f>E13/E3</f>
         <v>-6.8493157557677126E-2</v>
       </c>
-      <c r="F30" s="46">
+      <c r="F30" s="42">
         <f>F13/F3</f>
         <v>-0.10020521751030448</v>
       </c>
-      <c r="G30" s="47">
-        <f t="shared" ref="G30:I30" si="56">G13/G3</f>
+      <c r="G30" s="42">
+        <f t="shared" ref="G30:I30" si="57">G13/G3</f>
         <v>-5.075702466463336E-2</v>
       </c>
-      <c r="H30" s="46">
-        <f t="shared" si="56"/>
+      <c r="H30" s="43">
+        <f t="shared" si="57"/>
+        <v>-3.1138471925184166E-2</v>
+      </c>
+      <c r="I30" s="42">
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="I30" s="46">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="L30" s="46">
-        <f t="shared" ref="L30:S30" si="57">L13/L3</f>
+      <c r="L30" s="42">
+        <f t="shared" ref="L30:S30" si="58">L13/L3</f>
         <v>-9.7395812949690505E-2</v>
       </c>
-      <c r="M30" s="46">
-        <f t="shared" si="57"/>
+      <c r="M30" s="42">
+        <f t="shared" si="58"/>
         <v>-0.11258468475211493</v>
       </c>
-      <c r="N30" s="46">
-        <f t="shared" si="57"/>
+      <c r="N30" s="42">
+        <f t="shared" si="58"/>
         <v>-0.1014405447666855</v>
       </c>
-      <c r="O30" s="46">
-        <f t="shared" si="57"/>
+      <c r="O30" s="42">
+        <f t="shared" si="58"/>
         <v>-9.232091670036538E-2</v>
       </c>
-      <c r="P30" s="46">
-        <f t="shared" si="57"/>
+      <c r="P30" s="42">
+        <f t="shared" si="58"/>
         <v>-8.6878686170398234E-2</v>
       </c>
-      <c r="Q30" s="46">
+      <c r="Q30" s="42">
         <f>Q13/Q3</f>
         <v>-5.2013770959220725E-2</v>
       </c>
-      <c r="R30" s="46">
+      <c r="R30" s="42">
         <f>R13/R3</f>
         <v>-4.7571581514890195E-2</v>
       </c>
-      <c r="S30" s="46">
-        <f t="shared" si="57"/>
+      <c r="S30" s="42">
+        <f t="shared" si="58"/>
         <v>-3.5033239648612068E-2</v>
       </c>
-      <c r="T30" s="46">
-        <f t="shared" ref="T30:U30" si="58">T13/T3</f>
+      <c r="T30" s="42">
+        <f t="shared" ref="T30:U30" si="59">T13/T3</f>
         <v>-2.7775659600427025E-2</v>
       </c>
-      <c r="U30" s="46">
-        <f t="shared" si="58"/>
+      <c r="U30" s="42">
+        <f t="shared" si="59"/>
         <v>-3.5470405868168832E-2</v>
       </c>
-      <c r="V30" s="47">
-        <f t="shared" ref="V30:Y30" si="59">V13/V3</f>
+      <c r="V30" s="42">
+        <f t="shared" ref="V30:Y30" si="60">V13/V3</f>
         <v>-3.3588479057501966E-2</v>
       </c>
-      <c r="W30" s="46" t="e">
-        <f t="shared" si="59"/>
+      <c r="W30" s="42">
+        <f t="shared" si="60"/>
+        <v>-2.8359346726316528E-2</v>
+      </c>
+      <c r="X30" s="43">
+        <f t="shared" si="60"/>
+        <v>-2.2244520027445976E-2</v>
+      </c>
+      <c r="Y30" s="42" t="e">
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X30" s="46" t="e">
-        <f t="shared" si="59"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y30" s="46" t="e">
-        <f t="shared" si="59"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="48">
-        <f t="shared" ref="C31:F31" si="60">-C13/C12</f>
+      <c r="C31" s="44">
+        <f t="shared" ref="C31:F31" si="61">-C13/C12</f>
         <v>-0.1541124283771651</v>
       </c>
-      <c r="D31" s="48">
-        <f t="shared" si="60"/>
+      <c r="D31" s="44">
+        <f t="shared" si="61"/>
         <v>-7.671907679879103E-2</v>
       </c>
-      <c r="E31" s="48">
-        <f t="shared" si="60"/>
+      <c r="E31" s="44">
+        <f t="shared" si="61"/>
         <v>-0.30247355291202405</v>
       </c>
-      <c r="F31" s="46">
-        <f t="shared" si="60"/>
+      <c r="F31" s="42">
+        <f t="shared" si="61"/>
         <v>0.71928340393491097</v>
       </c>
-      <c r="G31" s="47">
-        <f t="shared" ref="G31:I31" si="61">-G13/G12</f>
+      <c r="G31" s="42">
+        <f t="shared" ref="G31:I31" si="62">-G13/G12</f>
         <v>0.16732385305731867</v>
       </c>
-      <c r="H31" s="46">
-        <f t="shared" si="61"/>
+      <c r="H31" s="43">
+        <f t="shared" si="62"/>
+        <v>7.9309233040517235E-2</v>
+      </c>
+      <c r="I31" s="42">
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
-      <c r="I31" s="46">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="L31" s="48">
-        <f t="shared" ref="L31:S31" si="62">-L13/L12</f>
+      <c r="L31" s="44">
+        <f t="shared" ref="L31:S31" si="63">-L13/L12</f>
         <v>0.62307933440481045</v>
       </c>
-      <c r="M31" s="48">
-        <f t="shared" si="62"/>
+      <c r="M31" s="44">
+        <f t="shared" si="63"/>
         <v>1.0452144147237079</v>
       </c>
-      <c r="N31" s="48">
-        <f t="shared" si="62"/>
+      <c r="N31" s="44">
+        <f t="shared" si="63"/>
         <v>0.77447766201940493</v>
       </c>
-      <c r="O31" s="48">
-        <f t="shared" si="62"/>
+      <c r="O31" s="44">
+        <f t="shared" si="63"/>
         <v>0.58880572040137491</v>
       </c>
-      <c r="P31" s="48">
-        <f t="shared" si="62"/>
+      <c r="P31" s="44">
+        <f t="shared" si="63"/>
         <v>0.2950157709005724</v>
       </c>
-      <c r="Q31" s="46">
+      <c r="Q31" s="42">
         <f>-Q13/Q12</f>
         <v>0.1743258132936672</v>
       </c>
-      <c r="R31" s="46">
-        <f t="shared" si="62"/>
+      <c r="R31" s="42">
+        <f t="shared" si="63"/>
         <v>0.15968382966580907</v>
       </c>
-      <c r="S31" s="46">
-        <f t="shared" si="62"/>
+      <c r="S31" s="42">
+        <f t="shared" si="63"/>
         <v>0.11146848377981249</v>
       </c>
-      <c r="T31" s="46">
-        <f t="shared" ref="T31:U31" si="63">-T13/T12</f>
+      <c r="T31" s="42">
+        <f t="shared" ref="T31:U31" si="64">-T13/T12</f>
         <v>5.8402645555666911E-2</v>
       </c>
-      <c r="U31" s="46">
-        <f t="shared" si="63"/>
+      <c r="U31" s="42">
+        <f t="shared" si="64"/>
         <v>9.7018234218256394E-2</v>
       </c>
-      <c r="V31" s="47">
-        <f t="shared" ref="V31:Y31" si="64">-V13/V12</f>
+      <c r="V31" s="42">
+        <f t="shared" ref="V31:Y31" si="65">-V13/V12</f>
         <v>0.11031748263547142</v>
       </c>
-      <c r="W31" s="46" t="e">
-        <f t="shared" si="64"/>
+      <c r="W31" s="42">
+        <f t="shared" si="65"/>
+        <v>6.6664253262620599E-2</v>
+      </c>
+      <c r="X31" s="43">
+        <f t="shared" si="65"/>
+        <v>4.3672866330610127E-2</v>
+      </c>
+      <c r="Y31" s="42" t="e">
+        <f t="shared" si="65"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X31" s="46" t="e">
-        <f t="shared" si="64"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y31" s="46" t="e">
-        <f t="shared" si="64"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="G32" s="12">
+    </row>
+    <row r="32" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="G32" s="156">
         <f>G22*G20/H20</f>
-        <v>1.1129767037129192</v>
+        <v>1.1262723911705461</v>
       </c>
     </row>
     <row r="34" spans="2:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -18574,55 +18803,59 @@
         <v>30</v>
       </c>
       <c r="C34" s="10">
-        <f t="shared" ref="C34:E34" si="65">C35-C56-C58</f>
+        <f t="shared" ref="C34:E34" si="66">C35-C56-C58</f>
         <v>42.988823999999994</v>
       </c>
       <c r="D34" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>-0.97740299999999536</v>
       </c>
       <c r="E34" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>4.2520639999999972</v>
       </c>
       <c r="F34" s="10">
         <f>F35-F56-F58</f>
         <v>67.374212</v>
       </c>
-      <c r="G34" s="13">
+      <c r="G34" s="162">
         <f>G35-G56-G58</f>
         <v>-30.80630699999999</v>
       </c>
+      <c r="H34" s="13">
+        <f>H35-H56-H58</f>
+        <v>-75.937000000000012</v>
+      </c>
       <c r="L34" s="10">
-        <f t="shared" ref="L34" si="66">L35-L56-L58</f>
+        <f t="shared" ref="L34" si="67">L35-L56-L58</f>
         <v>0</v>
       </c>
       <c r="M34" s="10">
-        <f t="shared" ref="M34" si="67">M35-M56-M58</f>
+        <f t="shared" ref="M34" si="68">M35-M56-M58</f>
         <v>0</v>
       </c>
       <c r="N34" s="10">
-        <f t="shared" ref="N34" si="68">N35-N56-N58</f>
+        <f t="shared" ref="N34" si="69">N35-N56-N58</f>
         <v>-10.23635800000001</v>
       </c>
       <c r="O34" s="10">
-        <f t="shared" ref="O34" si="69">O35-O56-O58</f>
+        <f t="shared" ref="O34" si="70">O35-O56-O58</f>
         <v>67.374212</v>
       </c>
       <c r="P34" s="10">
-        <f t="shared" ref="P34" si="70">P35-P56-P58</f>
+        <f t="shared" ref="P34" si="71">P35-P56-P58</f>
         <v>6.0957769999999982</v>
       </c>
       <c r="Q34" s="10">
-        <f t="shared" ref="Q34" si="71">Q35-Q56-Q58</f>
+        <f t="shared" ref="Q34" si="72">Q35-Q56-Q58</f>
         <v>-10.855995</v>
       </c>
       <c r="R34" s="10">
-        <f t="shared" ref="R34:Z34" si="72">R35-R56-R58</f>
+        <f t="shared" ref="R34:Z34" si="73">R35-R56-R58</f>
         <v>-13.875219000000001</v>
       </c>
       <c r="S34" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>-30.80630699999999</v>
       </c>
       <c r="T34" s="10">
@@ -18630,27 +18863,27 @@
         <v>19.003</v>
       </c>
       <c r="U34" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>-41.558000000000007</v>
       </c>
-      <c r="V34" s="13">
+      <c r="V34" s="162">
         <f>V35-V56-V58</f>
         <v>-13.164999999999992</v>
       </c>
       <c r="W34" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
+        <v>-75.937000000000012</v>
+      </c>
+      <c r="X34" s="13">
+        <f t="shared" si="73"/>
+        <v>-23.924000000000021</v>
+      </c>
+      <c r="Y34" s="10">
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
-      <c r="X34" s="10">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="10">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
       <c r="Z34" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
     </row>
@@ -18670,16 +18903,20 @@
       <c r="F35" s="9">
         <v>67.624212</v>
       </c>
-      <c r="G35" s="14">
+      <c r="G35" s="163">
         <v>73.185252000000006</v>
+      </c>
+      <c r="H35" s="14">
+        <f>W35</f>
+        <v>64.054000000000002</v>
       </c>
       <c r="L35" s="9"/>
       <c r="M35" s="9"/>
-      <c r="N35" s="122">
+      <c r="N35" s="118">
         <v>65.150279999999995</v>
       </c>
       <c r="O35" s="9">
-        <f t="shared" ref="O35:O40" si="73">F35</f>
+        <f t="shared" ref="O35:O40" si="74">F35</f>
         <v>67.624212</v>
       </c>
       <c r="P35" s="9">
@@ -18701,8 +18938,14 @@
       <c r="U35" s="9">
         <v>88.942999999999998</v>
       </c>
-      <c r="V35" s="14">
+      <c r="V35" s="163">
         <v>104.14700000000001</v>
+      </c>
+      <c r="W35" s="166">
+        <v>64.054000000000002</v>
+      </c>
+      <c r="X35" s="14">
+        <v>120.44799999999999</v>
       </c>
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.25">
@@ -18721,16 +18964,20 @@
       <c r="F36" s="9">
         <v>2.9930110000000001</v>
       </c>
-      <c r="G36" s="14">
+      <c r="G36" s="163">
         <v>4.8495819999999998</v>
+      </c>
+      <c r="H36" s="14">
+        <f t="shared" ref="H36:H60" si="75">W36</f>
+        <v>8.4130000000000003</v>
       </c>
       <c r="L36" s="9"/>
       <c r="M36" s="9"/>
-      <c r="N36" s="122">
+      <c r="N36" s="118">
         <v>1.5804180000000001</v>
       </c>
       <c r="O36" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>2.9930110000000001</v>
       </c>
       <c r="P36" s="9">
@@ -18743,7 +18990,7 @@
         <v>7.1733260000000003</v>
       </c>
       <c r="S36" s="9">
-        <f t="shared" ref="S36:S40" si="74">G36</f>
+        <f t="shared" ref="S36:S40" si="76">G36</f>
         <v>4.8495819999999998</v>
       </c>
       <c r="T36" s="9">
@@ -18752,8 +18999,14 @@
       <c r="U36" s="9">
         <v>10.558999999999999</v>
       </c>
-      <c r="V36" s="14">
+      <c r="V36" s="163">
         <v>10.914999999999999</v>
+      </c>
+      <c r="W36" s="166">
+        <v>8.4130000000000003</v>
+      </c>
+      <c r="X36" s="14">
+        <v>4.7450000000000001</v>
       </c>
     </row>
     <row r="37" spans="2:26" x14ac:dyDescent="0.25">
@@ -18772,16 +19025,20 @@
       <c r="F37" s="9">
         <v>142.885682</v>
       </c>
-      <c r="G37" s="14">
+      <c r="G37" s="163">
         <v>190.665266</v>
+      </c>
+      <c r="H37" s="14">
+        <f t="shared" si="75"/>
+        <v>283.39999999999998</v>
       </c>
       <c r="L37" s="9"/>
       <c r="M37" s="9"/>
-      <c r="N37" s="122">
+      <c r="N37" s="118">
         <v>111.146024</v>
       </c>
       <c r="O37" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>142.885682</v>
       </c>
       <c r="P37" s="9">
@@ -18794,7 +19051,7 @@
         <v>151.41349</v>
       </c>
       <c r="S37" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>190.665266</v>
       </c>
       <c r="T37" s="9">
@@ -18803,8 +19060,14 @@
       <c r="U37" s="9">
         <v>208.55500000000001</v>
       </c>
-      <c r="V37" s="14">
+      <c r="V37" s="163">
         <v>217.84899999999999</v>
+      </c>
+      <c r="W37" s="166">
+        <v>283.39999999999998</v>
+      </c>
+      <c r="X37" s="14">
+        <v>282.76100000000002</v>
       </c>
     </row>
     <row r="38" spans="2:26" x14ac:dyDescent="0.25">
@@ -18819,16 +19082,20 @@
       <c r="F38" s="9">
         <v>-12.253041</v>
       </c>
-      <c r="G38" s="14">
+      <c r="G38" s="163">
         <v>-26.103421000000001</v>
+      </c>
+      <c r="H38" s="14">
+        <f t="shared" si="75"/>
+        <v>-28.504999999999999</v>
       </c>
       <c r="L38" s="9"/>
       <c r="M38" s="9"/>
-      <c r="N38" s="122">
+      <c r="N38" s="118">
         <v>-8.5979419999999998</v>
       </c>
       <c r="O38" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>-12.253041</v>
       </c>
       <c r="P38" s="9">
@@ -18841,7 +19108,7 @@
         <v>-18.626221999999999</v>
       </c>
       <c r="S38" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>-26.103421000000001</v>
       </c>
       <c r="T38" s="9">
@@ -18850,8 +19117,14 @@
       <c r="U38" s="9">
         <v>-23.614999999999998</v>
       </c>
-      <c r="V38" s="14">
+      <c r="V38" s="163">
         <v>-33.718000000000004</v>
+      </c>
+      <c r="W38" s="166">
+        <v>-28.504999999999999</v>
+      </c>
+      <c r="X38" s="14">
+        <v>-19.794</v>
       </c>
     </row>
     <row r="39" spans="2:26" x14ac:dyDescent="0.25">
@@ -18870,8 +19143,12 @@
       <c r="F39" s="9">
         <v>1.571728</v>
       </c>
-      <c r="G39" s="14">
+      <c r="G39" s="163">
         <v>3.6291820000000001</v>
+      </c>
+      <c r="H39" s="14">
+        <f t="shared" si="75"/>
+        <v>6.1859999999999999</v>
       </c>
       <c r="L39" s="9"/>
       <c r="M39" s="9"/>
@@ -18879,7 +19156,7 @@
         <v>2.0556489999999998</v>
       </c>
       <c r="O39" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>1.571728</v>
       </c>
       <c r="P39" s="9">
@@ -18892,7 +19169,7 @@
         <v>3.82328</v>
       </c>
       <c r="S39" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>3.6291820000000001</v>
       </c>
       <c r="T39" s="9">
@@ -18901,8 +19178,14 @@
       <c r="U39" s="9">
         <v>4.0250000000000004</v>
       </c>
-      <c r="V39" s="14">
+      <c r="V39" s="163">
         <v>7.423</v>
+      </c>
+      <c r="W39" s="166">
+        <v>6.1859999999999999</v>
+      </c>
+      <c r="X39" s="14">
+        <v>23.03</v>
       </c>
     </row>
     <row r="40" spans="2:26" x14ac:dyDescent="0.25">
@@ -18921,8 +19204,12 @@
       <c r="F40" s="9">
         <v>6.223274</v>
       </c>
-      <c r="G40" s="14">
+      <c r="G40" s="163">
         <v>11.392782</v>
+      </c>
+      <c r="H40" s="14">
+        <f t="shared" si="75"/>
+        <v>18.315999999999999</v>
       </c>
       <c r="L40" s="9"/>
       <c r="M40" s="9"/>
@@ -18930,7 +19217,7 @@
         <v>4.8685590000000003</v>
       </c>
       <c r="O40" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>6.223274</v>
       </c>
       <c r="P40" s="9">
@@ -18943,7 +19230,7 @@
         <v>8.5809859999999993</v>
       </c>
       <c r="S40" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>11.392782</v>
       </c>
       <c r="T40" s="9">
@@ -18952,16 +19239,20 @@
       <c r="U40" s="9">
         <v>23.065999999999999</v>
       </c>
-      <c r="V40" s="14">
+      <c r="V40" s="163">
         <v>22.838000000000001</v>
       </c>
+      <c r="W40" s="166">
+        <v>18.315999999999999</v>
+      </c>
+      <c r="X40" s="14"/>
     </row>
     <row r="41" spans="2:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C41" s="10">
-        <f t="shared" ref="C41" si="75">SUM(C35:C40)</f>
+        <f t="shared" ref="C41" si="77">SUM(C35:C40)</f>
         <v>173.00042799999997</v>
       </c>
       <c r="D41" s="10">
@@ -18969,75 +19260,79 @@
         <v>221.29090299999999</v>
       </c>
       <c r="E41" s="10">
-        <f t="shared" ref="E41:G41" si="76">SUM(E35:E40)</f>
+        <f t="shared" ref="E41:H41" si="78">SUM(E35:E40)</f>
         <v>170.13146</v>
       </c>
       <c r="F41" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>209.04486600000001</v>
       </c>
-      <c r="G41" s="13">
-        <f t="shared" si="76"/>
+      <c r="G41" s="162">
+        <f t="shared" si="78"/>
         <v>257.61864300000002</v>
       </c>
+      <c r="H41" s="13">
+        <f t="shared" si="78"/>
+        <v>351.86399999999992</v>
+      </c>
       <c r="L41" s="10">
-        <f t="shared" ref="L41:V41" si="77">SUM(L35:L40)</f>
+        <f t="shared" ref="L41:V41" si="79">SUM(L35:L40)</f>
         <v>0</v>
       </c>
       <c r="M41" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="N41" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>176.20298799999998</v>
       </c>
       <c r="O41" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>209.04486600000001</v>
       </c>
       <c r="P41" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>191.68395899999999</v>
       </c>
       <c r="Q41" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>190.470189</v>
       </c>
       <c r="R41" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>232.42736500000001</v>
       </c>
       <c r="S41" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>257.61864300000002</v>
       </c>
       <c r="T41" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>265.94500000000005</v>
       </c>
       <c r="U41" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>311.53299999999996</v>
       </c>
-      <c r="V41" s="13">
-        <f t="shared" si="77"/>
+      <c r="V41" s="162">
+        <f t="shared" si="79"/>
         <v>329.45400000000001</v>
       </c>
       <c r="W41" s="10">
-        <f t="shared" ref="W41:Z41" si="78">SUM(W35:W40)</f>
+        <f t="shared" ref="W41:Z41" si="80">SUM(W35:W40)</f>
+        <v>351.86399999999992</v>
+      </c>
+      <c r="X41" s="13">
+        <f t="shared" si="80"/>
+        <v>411.19000000000005</v>
+      </c>
+      <c r="Y41" s="10">
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
-      <c r="X41" s="10">
-        <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="Y41" s="10">
-        <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
       <c r="Z41" s="10">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
     </row>
@@ -19057,8 +19352,12 @@
       <c r="F42" s="9">
         <v>1.8984700000000001</v>
       </c>
-      <c r="G42" s="14">
+      <c r="G42" s="163">
         <v>2.441611</v>
+      </c>
+      <c r="H42" s="14">
+        <f t="shared" si="75"/>
+        <v>3.331</v>
       </c>
       <c r="L42" s="9"/>
       <c r="M42" s="9"/>
@@ -19079,7 +19378,7 @@
         <v>2.2892269999999999</v>
       </c>
       <c r="S42" s="9">
-        <f t="shared" ref="S42:S46" si="79">G42</f>
+        <f t="shared" ref="S42:S46" si="81">G42</f>
         <v>2.441611</v>
       </c>
       <c r="T42" s="9">
@@ -19088,11 +19387,15 @@
       <c r="U42" s="9">
         <v>2.7770000000000001</v>
       </c>
-      <c r="V42" s="14">
+      <c r="V42" s="163">
         <v>3.0939999999999999</v>
       </c>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
+      <c r="W42" s="9">
+        <v>3.331</v>
+      </c>
+      <c r="X42" s="14">
+        <v>3.7429999999999999</v>
+      </c>
       <c r="Y42" s="9"/>
       <c r="Z42" s="9"/>
     </row>
@@ -19114,8 +19417,12 @@
       <c r="F43" s="9">
         <v>0.99447600000000003</v>
       </c>
-      <c r="G43" s="14">
+      <c r="G43" s="163">
         <v>0.80042400000000002</v>
+      </c>
+      <c r="H43" s="14">
+        <f t="shared" si="75"/>
+        <v>0.66500000000000004</v>
       </c>
       <c r="L43" s="9"/>
       <c r="M43" s="9"/>
@@ -19136,7 +19443,7 @@
         <v>0.834117</v>
       </c>
       <c r="S43" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0.80042400000000002</v>
       </c>
       <c r="T43" s="9">
@@ -19145,11 +19452,15 @@
       <c r="U43" s="9">
         <v>0.73499999999999999</v>
       </c>
-      <c r="V43" s="14">
+      <c r="V43" s="163">
         <v>0.7</v>
       </c>
-      <c r="W43" s="9"/>
-      <c r="X43" s="9"/>
+      <c r="W43" s="9">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="X43" s="14">
+        <v>0.628</v>
+      </c>
       <c r="Y43" s="9"/>
       <c r="Z43" s="9"/>
     </row>
@@ -19169,8 +19480,12 @@
       <c r="F44" s="9">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="G44" s="14">
+      <c r="G44" s="163">
         <v>20.275310000000001</v>
+      </c>
+      <c r="H44" s="14">
+        <f t="shared" si="75"/>
+        <v>30.134</v>
       </c>
       <c r="L44" s="9"/>
       <c r="M44" s="9"/>
@@ -19191,7 +19506,7 @@
         <v>1.1072979999999999</v>
       </c>
       <c r="S44" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>20.275310000000001</v>
       </c>
       <c r="T44" s="9">
@@ -19200,11 +19515,15 @@
       <c r="U44" s="9">
         <v>20.466999999999999</v>
       </c>
-      <c r="V44" s="14">
+      <c r="V44" s="163">
         <v>19.594000000000001</v>
       </c>
-      <c r="W44" s="9"/>
-      <c r="X44" s="9"/>
+      <c r="W44" s="9">
+        <v>30.134</v>
+      </c>
+      <c r="X44" s="14">
+        <v>22.193000000000001</v>
+      </c>
       <c r="Y44" s="9"/>
       <c r="Z44" s="9"/>
     </row>
@@ -19216,8 +19535,12 @@
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
-      <c r="G45" s="14">
+      <c r="G45" s="163">
         <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <f t="shared" si="75"/>
+        <v>13.615</v>
       </c>
       <c r="L45" s="9"/>
       <c r="M45" s="9"/>
@@ -19233,7 +19556,7 @@
         <v>15.86379</v>
       </c>
       <c r="S45" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="T45" s="9">
@@ -19242,11 +19565,15 @@
       <c r="U45" s="9">
         <v>14.42</v>
       </c>
-      <c r="V45" s="14">
+      <c r="V45" s="163">
         <v>13.443</v>
       </c>
-      <c r="W45" s="9"/>
-      <c r="X45" s="9"/>
+      <c r="W45" s="9">
+        <v>13.615</v>
+      </c>
+      <c r="X45" s="14">
+        <v>15.721</v>
+      </c>
       <c r="Y45" s="9"/>
       <c r="Z45" s="9"/>
     </row>
@@ -19266,8 +19593,12 @@
       <c r="F46" s="9">
         <v>0.625471</v>
       </c>
-      <c r="G46" s="14">
+      <c r="G46" s="163">
         <v>0.625471</v>
+      </c>
+      <c r="H46" s="14">
+        <f t="shared" si="75"/>
+        <v>0.62</v>
       </c>
       <c r="L46" s="9"/>
       <c r="M46" s="9"/>
@@ -19288,7 +19619,7 @@
         <v>0.34747499999999998</v>
       </c>
       <c r="S46" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0.625471</v>
       </c>
       <c r="T46" s="9">
@@ -19297,11 +19628,15 @@
       <c r="U46" s="9">
         <v>0.62</v>
       </c>
-      <c r="V46" s="14">
+      <c r="V46" s="163">
         <v>0.67900000000000005</v>
       </c>
-      <c r="W46" s="9"/>
-      <c r="X46" s="9"/>
+      <c r="W46" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="X46" s="14">
+        <v>0.83</v>
+      </c>
       <c r="Y46" s="9"/>
       <c r="Z46" s="9"/>
     </row>
@@ -19325,68 +19660,72 @@
         <f>SUM(F41:F46)</f>
         <v>212.64528300000001</v>
       </c>
-      <c r="G47" s="13">
+      <c r="G47" s="162">
         <f>SUM(G41:G46)</f>
         <v>281.76145900000006</v>
       </c>
+      <c r="H47" s="13">
+        <f>SUM(H41:H46)</f>
+        <v>400.22899999999998</v>
+      </c>
       <c r="L47" s="10">
-        <f t="shared" ref="L47:V47" si="80">SUM(L41:L46)</f>
+        <f t="shared" ref="L47:V47" si="82">SUM(L41:L46)</f>
         <v>0</v>
       </c>
       <c r="M47" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N47" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>179.90335899999999</v>
       </c>
       <c r="O47" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>212.64528300000001</v>
       </c>
       <c r="P47" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>195.70842099999999</v>
       </c>
       <c r="Q47" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>212.07665299999999</v>
       </c>
       <c r="R47" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>252.869272</v>
       </c>
       <c r="S47" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>281.76145900000006</v>
       </c>
       <c r="T47" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>298.07400000000001</v>
       </c>
       <c r="U47" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>350.55199999999996</v>
       </c>
-      <c r="V47" s="13">
-        <f t="shared" si="80"/>
+      <c r="V47" s="162">
+        <f t="shared" si="82"/>
         <v>366.96399999999994</v>
       </c>
       <c r="W47" s="10">
-        <f t="shared" ref="W47:Z47" si="81">SUM(W41:W46)</f>
+        <f t="shared" ref="W47:Z47" si="83">SUM(W41:W46)</f>
+        <v>400.22899999999998</v>
+      </c>
+      <c r="X47" s="13">
+        <f t="shared" si="83"/>
+        <v>454.30500000000001</v>
+      </c>
+      <c r="Y47" s="10">
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
-      <c r="X47" s="10">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="Y47" s="10">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
       <c r="Z47" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
     </row>
@@ -19406,8 +19745,12 @@
       <c r="F48" s="9">
         <v>74.135491000000002</v>
       </c>
-      <c r="G48" s="14">
+      <c r="G48" s="163">
         <v>68.966677000000004</v>
+      </c>
+      <c r="H48" s="14">
+        <f t="shared" si="75"/>
+        <v>56.374000000000002</v>
       </c>
       <c r="L48" s="9"/>
       <c r="M48" s="9"/>
@@ -19415,7 +19758,7 @@
         <v>68.182563000000002</v>
       </c>
       <c r="O48" s="9">
-        <f t="shared" ref="O48:O52" si="82">F48</f>
+        <f t="shared" ref="O48:O52" si="84">F48</f>
         <v>74.135491000000002</v>
       </c>
       <c r="P48" s="9">
@@ -19428,7 +19771,7 @@
         <v>70.449314000000001</v>
       </c>
       <c r="S48" s="9">
-        <f t="shared" ref="S48:S54" si="83">G48</f>
+        <f t="shared" ref="S48:S54" si="85">G48</f>
         <v>68.966677000000004</v>
       </c>
       <c r="T48" s="9">
@@ -19437,11 +19780,15 @@
       <c r="U48" s="9">
         <v>60.478000000000002</v>
       </c>
-      <c r="V48" s="14">
+      <c r="V48" s="163">
         <v>57.829000000000001</v>
       </c>
-      <c r="W48" s="9"/>
-      <c r="X48" s="9"/>
+      <c r="W48" s="9">
+        <v>56.374000000000002</v>
+      </c>
+      <c r="X48" s="14">
+        <v>57.567999999999998</v>
+      </c>
       <c r="Y48" s="9"/>
       <c r="Z48" s="9"/>
     </row>
@@ -19461,14 +19808,18 @@
       <c r="F49" s="9">
         <v>5.7315999999999999E-2</v>
       </c>
-      <c r="G49" s="14"/>
+      <c r="G49" s="163"/>
+      <c r="H49" s="14">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
       <c r="L49" s="9"/>
       <c r="M49" s="9"/>
       <c r="N49" s="9">
         <v>5.2116999999999997E-2</v>
       </c>
       <c r="O49" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>5.7315999999999999E-2</v>
       </c>
       <c r="P49" s="9">
@@ -19481,14 +19832,14 @@
         <v>8.3222000000000004E-2</v>
       </c>
       <c r="S49" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="T49" s="9"/>
       <c r="U49" s="9"/>
-      <c r="V49" s="14"/>
+      <c r="V49" s="163"/>
       <c r="W49" s="9"/>
-      <c r="X49" s="9"/>
+      <c r="X49" s="14"/>
       <c r="Y49" s="9"/>
       <c r="Z49" s="9"/>
     </row>
@@ -19508,14 +19859,18 @@
       <c r="F50" s="9">
         <v>10.790308</v>
       </c>
-      <c r="G50" s="14"/>
+      <c r="G50" s="163"/>
+      <c r="H50" s="14">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
       <c r="L50" s="9"/>
       <c r="M50" s="9"/>
       <c r="N50" s="9">
         <v>7.8326510000000003</v>
       </c>
       <c r="O50" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>10.790308</v>
       </c>
       <c r="P50" s="9">
@@ -19528,14 +19883,14 @@
         <v>11.475161999999999</v>
       </c>
       <c r="S50" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="T50" s="9"/>
       <c r="U50" s="9"/>
-      <c r="V50" s="14"/>
+      <c r="V50" s="163"/>
       <c r="W50" s="9"/>
-      <c r="X50" s="9"/>
+      <c r="X50" s="14"/>
       <c r="Y50" s="9"/>
       <c r="Z50" s="9"/>
     </row>
@@ -19555,8 +19910,12 @@
       <c r="F51" s="9">
         <v>5.2614359999999998</v>
       </c>
-      <c r="G51" s="14">
+      <c r="G51" s="163">
         <v>7.4554159999999996</v>
+      </c>
+      <c r="H51" s="14">
+        <f t="shared" si="75"/>
+        <v>6.9080000000000004</v>
       </c>
       <c r="L51" s="9"/>
       <c r="M51" s="9"/>
@@ -19564,7 +19923,7 @@
         <v>5.300675</v>
       </c>
       <c r="O51" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>5.2614359999999998</v>
       </c>
       <c r="P51" s="9">
@@ -19577,7 +19936,7 @@
         <v>10.498376</v>
       </c>
       <c r="S51" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>7.4554159999999996</v>
       </c>
       <c r="T51" s="9">
@@ -19586,11 +19945,15 @@
       <c r="U51" s="9">
         <v>2.8279999999999998</v>
       </c>
-      <c r="V51" s="14">
+      <c r="V51" s="163">
         <v>6.4219999999999997</v>
       </c>
-      <c r="W51" s="9"/>
-      <c r="X51" s="9"/>
+      <c r="W51" s="9">
+        <v>6.9080000000000004</v>
+      </c>
+      <c r="X51" s="14">
+        <v>21.969000000000001</v>
+      </c>
       <c r="Y51" s="9"/>
       <c r="Z51" s="9"/>
     </row>
@@ -19606,8 +19969,12 @@
       <c r="F52" s="9">
         <v>2.64323</v>
       </c>
-      <c r="G52" s="14">
+      <c r="G52" s="163">
         <v>4.2342240000000002</v>
+      </c>
+      <c r="H52" s="14">
+        <f t="shared" si="75"/>
+        <v>5.431</v>
       </c>
       <c r="L52" s="9"/>
       <c r="M52" s="9"/>
@@ -19615,7 +19982,7 @@
         <v>2.0702310000000002</v>
       </c>
       <c r="O52" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>2.64323</v>
       </c>
       <c r="P52" s="9">
@@ -19628,7 +19995,7 @@
         <v>4.3732699999999998</v>
       </c>
       <c r="S52" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>4.2342240000000002</v>
       </c>
       <c r="T52" s="9">
@@ -19637,11 +20004,15 @@
       <c r="U52" s="9">
         <v>4.2610000000000001</v>
       </c>
-      <c r="V52" s="14">
+      <c r="V52" s="163">
         <v>4.8449999999999998</v>
       </c>
-      <c r="W52" s="9"/>
-      <c r="X52" s="9"/>
+      <c r="W52" s="9">
+        <v>5.431</v>
+      </c>
+      <c r="X52" s="14">
+        <v>5.6689999999999996</v>
+      </c>
       <c r="Y52" s="9"/>
       <c r="Z52" s="9"/>
     </row>
@@ -19655,12 +20026,16 @@
       <c r="F53" s="9">
         <v>94.380905999999996</v>
       </c>
-      <c r="G53" s="14"/>
+      <c r="G53" s="163"/>
+      <c r="H53" s="14">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
       <c r="L53" s="9"/>
       <c r="M53" s="9"/>
       <c r="N53" s="9"/>
       <c r="O53" s="9">
-        <f t="shared" ref="O53" si="84">F53</f>
+        <f t="shared" ref="O53" si="86">F53</f>
         <v>94.380905999999996</v>
       </c>
       <c r="P53" s="9"/>
@@ -19669,14 +20044,14 @@
         <v>0</v>
       </c>
       <c r="S53" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="T53" s="9"/>
       <c r="U53" s="9"/>
-      <c r="V53" s="14"/>
+      <c r="V53" s="163"/>
       <c r="W53" s="9"/>
-      <c r="X53" s="9"/>
+      <c r="X53" s="14"/>
       <c r="Y53" s="9"/>
       <c r="Z53" s="9"/>
     </row>
@@ -19687,8 +20062,12 @@
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
-      <c r="G54" s="14">
+      <c r="G54" s="163">
         <v>25.020935999999999</v>
+      </c>
+      <c r="H54" s="14">
+        <f t="shared" si="75"/>
+        <v>21.053000000000001</v>
       </c>
       <c r="L54" s="9"/>
       <c r="M54" s="9"/>
@@ -19700,7 +20079,7 @@
         <v>0</v>
       </c>
       <c r="S54" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>25.020935999999999</v>
       </c>
       <c r="T54" s="9">
@@ -19709,11 +20088,15 @@
       <c r="U54" s="9">
         <v>21.306999999999999</v>
       </c>
-      <c r="V54" s="14">
+      <c r="V54" s="163">
         <v>24.565999999999999</v>
       </c>
-      <c r="W54" s="9"/>
-      <c r="X54" s="9"/>
+      <c r="W54" s="9">
+        <v>21.053000000000001</v>
+      </c>
+      <c r="X54" s="14">
+        <v>27.396000000000001</v>
+      </c>
       <c r="Y54" s="9"/>
       <c r="Z54" s="9"/>
     </row>
@@ -19737,68 +20120,72 @@
         <f>SUM(F48:F54)</f>
         <v>187.268687</v>
       </c>
-      <c r="G55" s="13">
+      <c r="G55" s="162">
         <f>SUM(G48:G54)</f>
         <v>105.67725300000001</v>
       </c>
+      <c r="H55" s="13">
+        <f>SUM(H48:H54)</f>
+        <v>89.766000000000005</v>
+      </c>
       <c r="L55" s="10">
-        <f t="shared" ref="L55:V55" si="85">SUM(L48:L54)</f>
+        <f t="shared" ref="L55:V55" si="87">SUM(L48:L54)</f>
         <v>0</v>
       </c>
       <c r="M55" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="N55" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>83.438237000000001</v>
       </c>
       <c r="O55" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>187.268687</v>
       </c>
       <c r="P55" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>92.941540999999987</v>
       </c>
       <c r="Q55" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>91.946695000000005</v>
       </c>
       <c r="R55" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>96.879344000000017</v>
       </c>
       <c r="S55" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>105.67725300000001</v>
       </c>
       <c r="T55" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>101.599</v>
       </c>
       <c r="U55" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>88.874000000000009</v>
       </c>
-      <c r="V55" s="13">
-        <f t="shared" si="85"/>
+      <c r="V55" s="162">
+        <f t="shared" si="87"/>
         <v>93.662000000000006</v>
       </c>
       <c r="W55" s="10">
-        <f t="shared" ref="W55:Z55" si="86">SUM(W48:W54)</f>
+        <f t="shared" ref="W55:Z55" si="88">SUM(W48:W54)</f>
+        <v>89.766000000000005</v>
+      </c>
+      <c r="X55" s="13">
+        <f t="shared" si="88"/>
+        <v>112.602</v>
+      </c>
+      <c r="Y55" s="10">
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="X55" s="10">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-      <c r="Y55" s="10">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
       <c r="Z55" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
     </row>
@@ -19818,7 +20205,11 @@
       <c r="F56" s="9">
         <v>0.25</v>
       </c>
-      <c r="G56" s="14">
+      <c r="G56" s="163">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="L56" s="9"/>
@@ -19840,14 +20231,14 @@
         <v>0</v>
       </c>
       <c r="S56" s="9">
-        <f t="shared" ref="S56:S60" si="87">G56</f>
+        <f t="shared" ref="S56:S60" si="89">G56</f>
         <v>0</v>
       </c>
       <c r="T56" s="9"/>
       <c r="U56" s="9"/>
-      <c r="V56" s="14"/>
+      <c r="V56" s="163"/>
       <c r="W56" s="9"/>
-      <c r="X56" s="9"/>
+      <c r="X56" s="14"/>
       <c r="Y56" s="9"/>
       <c r="Z56" s="9"/>
     </row>
@@ -19863,8 +20254,12 @@
       <c r="F57" s="9">
         <v>0.98169200000000001</v>
       </c>
-      <c r="G57" s="14">
+      <c r="G57" s="163">
         <v>0.823071</v>
+      </c>
+      <c r="H57" s="14">
+        <f t="shared" si="75"/>
+        <v>0.66100000000000003</v>
       </c>
       <c r="L57" s="9"/>
       <c r="M57" s="9"/>
@@ -19885,7 +20280,7 @@
         <v>0.85450899999999996</v>
       </c>
       <c r="S57" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>0.823071</v>
       </c>
       <c r="T57" s="9">
@@ -19894,11 +20289,15 @@
       <c r="U57" s="9">
         <v>0.75900000000000001</v>
       </c>
-      <c r="V57" s="14">
+      <c r="V57" s="163">
         <v>0.71099999999999997</v>
       </c>
-      <c r="W57" s="9"/>
-      <c r="X57" s="9"/>
+      <c r="W57" s="9">
+        <v>0.66100000000000003</v>
+      </c>
+      <c r="X57" s="14">
+        <v>0.60899999999999999</v>
+      </c>
       <c r="Y57" s="9"/>
       <c r="Z57" s="9"/>
     </row>
@@ -19918,8 +20317,12 @@
       <c r="F58" s="9">
         <v>0</v>
       </c>
-      <c r="G58" s="14">
+      <c r="G58" s="163">
         <v>103.991559</v>
+      </c>
+      <c r="H58" s="14">
+        <f t="shared" si="75"/>
+        <v>139.99100000000001</v>
       </c>
       <c r="L58" s="9"/>
       <c r="M58" s="9"/>
@@ -19940,7 +20343,7 @@
         <v>93.937724000000003</v>
       </c>
       <c r="S58" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>103.991559</v>
       </c>
       <c r="T58" s="9">
@@ -19949,11 +20352,15 @@
       <c r="U58" s="9">
         <v>130.501</v>
       </c>
-      <c r="V58" s="14">
+      <c r="V58" s="163">
         <v>117.312</v>
       </c>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
+      <c r="W58" s="9">
+        <v>139.99100000000001</v>
+      </c>
+      <c r="X58" s="14">
+        <v>144.37200000000001</v>
+      </c>
       <c r="Y58" s="9"/>
       <c r="Z58" s="9"/>
     </row>
@@ -19969,7 +20376,11 @@
       <c r="F59" s="9">
         <v>0.96725700000000003</v>
       </c>
-      <c r="G59" s="14">
+      <c r="G59" s="163">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="L59" s="9"/>
@@ -19987,14 +20398,14 @@
         <v>0</v>
       </c>
       <c r="S59" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="T59" s="9"/>
       <c r="U59" s="9"/>
-      <c r="V59" s="14"/>
+      <c r="V59" s="163"/>
       <c r="W59" s="9"/>
-      <c r="X59" s="9"/>
+      <c r="X59" s="14"/>
       <c r="Y59" s="9"/>
       <c r="Z59" s="9"/>
     </row>
@@ -20010,8 +20421,12 @@
       <c r="F60" s="9">
         <v>1.083323</v>
       </c>
-      <c r="G60" s="14">
+      <c r="G60" s="163">
         <v>4.4742999999999998E-2</v>
+      </c>
+      <c r="H60" s="14">
+        <f t="shared" si="75"/>
+        <v>0</v>
       </c>
       <c r="L60" s="9"/>
       <c r="M60" s="9"/>
@@ -20032,7 +20447,7 @@
         <v>5.9680999999999998E-2</v>
       </c>
       <c r="S60" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>4.4742999999999998E-2</v>
       </c>
       <c r="T60" s="9">
@@ -20041,11 +20456,11 @@
       <c r="U60" s="9">
         <v>0.02</v>
       </c>
-      <c r="V60" s="14">
+      <c r="V60" s="163">
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="W60" s="9"/>
-      <c r="X60" s="9"/>
+      <c r="X60" s="14"/>
       <c r="Y60" s="9"/>
       <c r="Z60" s="9"/>
     </row>
@@ -20069,68 +20484,72 @@
         <f>SUM(F55:F60)</f>
         <v>190.55095900000001</v>
       </c>
-      <c r="G61" s="13">
+      <c r="G61" s="162">
         <f>SUM(G55:G60)</f>
         <v>210.53662600000001</v>
       </c>
+      <c r="H61" s="13">
+        <f>SUM(H55:H60)</f>
+        <v>230.41800000000001</v>
+      </c>
       <c r="L61" s="10">
-        <f t="shared" ref="L61:O61" si="88">SUM(L55:L60)</f>
+        <f t="shared" ref="L61:O61" si="90">SUM(L55:L60)</f>
         <v>0</v>
       </c>
       <c r="M61" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="N61" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>161.929304</v>
       </c>
       <c r="O61" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>190.55095900000001</v>
       </c>
       <c r="P61" s="10">
-        <f t="shared" ref="P61:Q61" si="89">SUM(P55:P60)</f>
+        <f t="shared" ref="P61:Q61" si="91">SUM(P55:P60)</f>
         <v>166.09502999999998</v>
       </c>
       <c r="Q61" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>161.78693800000002</v>
       </c>
       <c r="R61" s="10">
-        <f t="shared" ref="R61:V61" si="90">SUM(R55:R60)</f>
+        <f t="shared" ref="R61:V61" si="92">SUM(R55:R60)</f>
         <v>191.73125800000003</v>
       </c>
       <c r="S61" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>210.53662600000001</v>
       </c>
       <c r="T61" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>172.31200000000001</v>
       </c>
       <c r="U61" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>220.15400000000002</v>
       </c>
-      <c r="V61" s="13">
-        <f t="shared" si="90"/>
+      <c r="V61" s="162">
+        <f t="shared" si="92"/>
         <v>211.69399999999999</v>
       </c>
       <c r="W61" s="10">
-        <f t="shared" ref="W61:Z61" si="91">SUM(W55:W60)</f>
+        <f t="shared" ref="W61:Z61" si="93">SUM(W55:W60)</f>
+        <v>230.41800000000001</v>
+      </c>
+      <c r="X61" s="13">
+        <f t="shared" si="93"/>
+        <v>257.58300000000003</v>
+      </c>
+      <c r="Y61" s="10">
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
-      <c r="X61" s="10">
-        <f t="shared" si="91"/>
-        <v>0</v>
-      </c>
-      <c r="Y61" s="10">
-        <f t="shared" si="91"/>
-        <v>0</v>
-      </c>
       <c r="Z61" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
     </row>
@@ -20139,11 +20558,11 @@
         <v>67</v>
       </c>
       <c r="C62" s="9">
-        <f t="shared" ref="C62:D62" si="92">C47-C61</f>
+        <f t="shared" ref="C62:D62" si="94">C47-C61</f>
         <v>59.958416999999955</v>
       </c>
       <c r="D62" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>37.792038000000019</v>
       </c>
       <c r="E62" s="9">
@@ -20154,72 +20573,72 @@
         <f>F47-F61</f>
         <v>22.094324</v>
       </c>
-      <c r="G62" s="14">
+      <c r="G62" s="163">
         <f>G47-G61</f>
         <v>71.224833000000046</v>
       </c>
-      <c r="H62" s="9">
+      <c r="H62" s="14">
         <f>H47-H61</f>
+        <v>169.81099999999998</v>
+      </c>
+      <c r="L62" s="9">
+        <f t="shared" ref="L62:O62" si="95">L47-L61</f>
         <v>0</v>
       </c>
-      <c r="L62" s="9">
-        <f t="shared" ref="L62:O62" si="93">L47-L61</f>
+      <c r="M62" s="9">
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
-      <c r="M62" s="9">
-        <f t="shared" si="93"/>
+      <c r="N62" s="9">
+        <f t="shared" si="95"/>
+        <v>17.974054999999993</v>
+      </c>
+      <c r="O62" s="9">
+        <f t="shared" si="95"/>
+        <v>22.094324</v>
+      </c>
+      <c r="P62" s="9">
+        <f t="shared" ref="P62:Q62" si="96">P47-P61</f>
+        <v>29.613391000000007</v>
+      </c>
+      <c r="Q62" s="9">
+        <f t="shared" si="96"/>
+        <v>50.289714999999973</v>
+      </c>
+      <c r="R62" s="9">
+        <f t="shared" ref="R62:V62" si="97">R47-R61</f>
+        <v>61.13801399999997</v>
+      </c>
+      <c r="S62" s="9">
+        <f t="shared" si="97"/>
+        <v>71.224833000000046</v>
+      </c>
+      <c r="T62" s="9">
+        <f t="shared" si="97"/>
+        <v>125.762</v>
+      </c>
+      <c r="U62" s="9">
+        <f t="shared" si="97"/>
+        <v>130.39799999999994</v>
+      </c>
+      <c r="V62" s="163">
+        <f t="shared" si="97"/>
+        <v>155.26999999999995</v>
+      </c>
+      <c r="W62" s="9">
+        <f t="shared" ref="W62:Z62" si="98">W47-W61</f>
+        <v>169.81099999999998</v>
+      </c>
+      <c r="X62" s="14">
+        <f t="shared" si="98"/>
+        <v>196.72199999999998</v>
+      </c>
+      <c r="Y62" s="9">
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="N62" s="9">
-        <f t="shared" si="93"/>
-        <v>17.974054999999993</v>
-      </c>
-      <c r="O62" s="9">
-        <f t="shared" si="93"/>
-        <v>22.094324</v>
-      </c>
-      <c r="P62" s="9">
-        <f t="shared" ref="P62:Q62" si="94">P47-P61</f>
-        <v>29.613391000000007</v>
-      </c>
-      <c r="Q62" s="9">
-        <f t="shared" si="94"/>
-        <v>50.289714999999973</v>
-      </c>
-      <c r="R62" s="9">
-        <f t="shared" ref="R62:V62" si="95">R47-R61</f>
-        <v>61.13801399999997</v>
-      </c>
-      <c r="S62" s="9">
-        <f t="shared" si="95"/>
-        <v>71.224833000000046</v>
-      </c>
-      <c r="T62" s="9">
-        <f t="shared" si="95"/>
-        <v>125.762</v>
-      </c>
-      <c r="U62" s="9">
-        <f t="shared" si="95"/>
-        <v>130.39799999999994</v>
-      </c>
-      <c r="V62" s="14">
-        <f t="shared" si="95"/>
-        <v>155.26999999999995</v>
-      </c>
-      <c r="W62" s="9">
-        <f t="shared" ref="W62:Z62" si="96">W47-W61</f>
-        <v>0</v>
-      </c>
-      <c r="X62" s="9">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-      <c r="Y62" s="9">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
       <c r="Z62" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
     </row>
@@ -20227,31 +20646,36 @@
       <c r="B64" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C64" s="49"/>
-      <c r="D64" s="49"/>
-      <c r="E64" s="49"/>
-      <c r="F64" s="133"/>
-      <c r="G64" s="135">
+      <c r="C64" s="45"/>
+      <c r="D64" s="45"/>
+      <c r="E64" s="45"/>
+      <c r="F64" s="128"/>
+      <c r="G64" s="174">
         <f>G19/G62</f>
         <v>1.0892481418664739</v>
       </c>
-      <c r="H64" s="129" t="e">
+      <c r="H64" s="129">
         <f>H19/H62</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V64" s="15"/>
-    </row>
-    <row r="82" spans="7:22" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="G82" s="40"/>
-      <c r="V82" s="40"/>
-    </row>
-    <row r="83" spans="7:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="G83" s="15"/>
-      <c r="V83" s="15"/>
+        <v>0.71146580610207821</v>
+      </c>
+      <c r="V64" s="157"/>
+      <c r="X64" s="15"/>
+    </row>
+    <row r="82" spans="7:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G82" s="160"/>
+      <c r="H82" s="38"/>
+      <c r="V82" s="160"/>
+      <c r="X82" s="38"/>
+    </row>
+    <row r="83" spans="7:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G83" s="157"/>
+      <c r="H83" s="15"/>
+      <c r="V83" s="157"/>
+      <c r="X83" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D25:I25">
+  <conditionalFormatting sqref="D25:J25">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -20263,7 +20687,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D29:I29">
+  <conditionalFormatting sqref="D29:J29">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -20275,7 +20699,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P37:V37">
+  <conditionalFormatting sqref="P37:W37 W38:W40">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -20316,73 +20740,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B1" s="136">
+      <c r="B1" s="130">
         <v>45474</v>
       </c>
-      <c r="C1" s="136">
+      <c r="C1" s="130">
         <v>45505</v>
       </c>
-      <c r="D1" s="136">
+      <c r="D1" s="130">
         <v>45536</v>
       </c>
-      <c r="E1" s="136">
+      <c r="E1" s="130">
         <v>45566</v>
       </c>
-      <c r="F1" s="136">
+      <c r="F1" s="130">
         <v>45597</v>
       </c>
-      <c r="G1" s="136">
+      <c r="G1" s="130">
         <v>45627</v>
       </c>
-      <c r="H1" s="136">
+      <c r="H1" s="130">
         <v>45658</v>
       </c>
-      <c r="I1" s="136">
+      <c r="I1" s="130">
         <v>45689</v>
       </c>
-      <c r="J1" s="136">
+      <c r="J1" s="130">
         <v>45717</v>
       </c>
-      <c r="K1" s="136">
+      <c r="K1" s="130">
         <v>45748</v>
       </c>
-      <c r="L1" s="136">
+      <c r="L1" s="130">
         <v>45778</v>
       </c>
-      <c r="M1" s="136">
+      <c r="M1" s="130">
         <v>45809</v>
       </c>
-      <c r="N1" s="136">
+      <c r="N1" s="130">
         <v>45839</v>
       </c>
-      <c r="O1" s="136">
+      <c r="O1" s="130">
         <v>45870</v>
       </c>
-      <c r="P1" s="136">
+      <c r="P1" s="130">
         <v>45901</v>
       </c>
-      <c r="Q1" s="136">
+      <c r="Q1" s="130">
         <v>45931</v>
       </c>
-      <c r="R1" s="136">
+      <c r="R1" s="130">
         <v>45962</v>
       </c>
-      <c r="S1" s="136">
+      <c r="S1" s="130">
         <v>45992</v>
       </c>
-      <c r="T1" s="136">
+      <c r="T1" s="130">
         <v>46023</v>
       </c>
-      <c r="U1" s="136">
+      <c r="U1" s="130">
         <v>46054</v>
       </c>
-      <c r="V1" s="136">
+      <c r="V1" s="130">
         <v>46082</v>
       </c>
-      <c r="W1" s="136">
+      <c r="W1" s="130">
         <v>46113</v>
       </c>
-      <c r="X1" s="136">
+      <c r="X1" s="130">
         <v>46143</v>
       </c>
     </row>
@@ -20833,41 +21257,41 @@
       <c r="A5" t="s">
         <v>186</v>
       </c>
-      <c r="B5" s="131">
+      <c r="B5" s="126">
         <v>0.93799999999999994</v>
       </c>
-      <c r="C5" s="131"/>
-      <c r="D5" s="131">
+      <c r="C5" s="126"/>
+      <c r="D5" s="126">
         <v>0.94399999999999995</v>
       </c>
-      <c r="E5" s="131">
+      <c r="E5" s="126">
         <v>0.94699999999999995</v>
       </c>
-      <c r="F5" s="131">
+      <c r="F5" s="126">
         <v>0.95699999999999996</v>
       </c>
-      <c r="G5" s="131">
+      <c r="G5" s="126">
         <v>0.95299999999999996</v>
       </c>
-      <c r="H5" s="131">
+      <c r="H5" s="126">
         <v>0.95599999999999996</v>
       </c>
-      <c r="I5" s="131">
+      <c r="I5" s="126">
         <v>0.95499999999999996</v>
       </c>
-      <c r="J5" s="131">
+      <c r="J5" s="126">
         <v>0.95699999999999996</v>
       </c>
-      <c r="K5" s="131">
+      <c r="K5" s="126">
         <v>0.96</v>
       </c>
-      <c r="L5" s="131">
+      <c r="L5" s="126">
         <v>0.96199999999999997</v>
       </c>
-      <c r="M5" s="131">
+      <c r="M5" s="126">
         <v>0.96399999999999997</v>
       </c>
-      <c r="N5" s="131">
+      <c r="N5" s="126">
         <v>0.96599999999999997</v>
       </c>
     </row>
@@ -20971,43 +21395,43 @@
       <c r="A9" t="s">
         <v>189</v>
       </c>
-      <c r="B9" s="130"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="130"/>
-      <c r="E9" s="130"/>
-      <c r="F9" s="130">
+      <c r="B9" s="125"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="125">
         <f>F2/B2-1</f>
         <v>1.3863636363636362</v>
       </c>
-      <c r="G9" s="130" t="e">
+      <c r="G9" s="125" t="e">
         <f t="shared" ref="G9:I9" si="0">G2/C2-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H9" s="130">
+      <c r="H9" s="125">
         <f>H2/D2-1</f>
         <v>1.612676056338028</v>
       </c>
-      <c r="I9" s="130">
+      <c r="I9" s="125">
         <f t="shared" si="0"/>
         <v>1.75</v>
       </c>
-      <c r="J9" s="130">
+      <c r="J9" s="125">
         <f t="shared" ref="J9" si="1">J2/F2-1</f>
         <v>1.519047619047619</v>
       </c>
-      <c r="K9" s="130">
+      <c r="K9" s="125">
         <f t="shared" ref="K9" si="2">K2/G2-1</f>
         <v>1.3029315960912053</v>
       </c>
-      <c r="L9" s="130">
+      <c r="L9" s="125">
         <f t="shared" ref="L9:N9" si="3">L2/H2-1</f>
         <v>0.77358490566037741</v>
       </c>
-      <c r="M9" s="130">
+      <c r="M9" s="125">
         <f t="shared" si="3"/>
         <v>0.61904761904761907</v>
       </c>
-      <c r="N9" s="130">
+      <c r="N9" s="125">
         <f t="shared" si="3"/>
         <v>0.48204158790170126</v>
       </c>
@@ -21016,43 +21440,43 @@
       <c r="A10" t="s">
         <v>190</v>
       </c>
-      <c r="B10" s="130"/>
-      <c r="C10" s="130"/>
-      <c r="D10" s="130"/>
-      <c r="E10" s="130"/>
-      <c r="F10" s="130">
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="125">
         <f>F7/B7-1</f>
         <v>0.24891067538126355</v>
       </c>
-      <c r="G10" s="130" t="e">
+      <c r="G10" s="125" t="e">
         <f t="shared" ref="G10:I10" si="4">G7/C7-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H10" s="130">
+      <c r="H10" s="125">
         <f t="shared" si="4"/>
         <v>0.4591309632330598</v>
       </c>
-      <c r="I10" s="130">
+      <c r="I10" s="125">
         <f t="shared" si="4"/>
         <v>0.47308699447192315</v>
       </c>
-      <c r="J10" s="130">
+      <c r="J10" s="125">
         <f t="shared" ref="J10" si="5">J7/F7-1</f>
         <v>0.36153510684692547</v>
       </c>
-      <c r="K10" s="130">
+      <c r="K10" s="125">
         <f t="shared" ref="K10" si="6">K7/G7-1</f>
         <v>0.33761342235918512</v>
       </c>
-      <c r="L10" s="130">
+      <c r="L10" s="125">
         <f t="shared" ref="L10:N10" si="7">L7/H7-1</f>
         <v>0.52269887546855487</v>
       </c>
-      <c r="M10" s="130">
+      <c r="M10" s="125">
         <f t="shared" si="7"/>
         <v>0.62630851273948251</v>
       </c>
-      <c r="N10" s="130">
+      <c r="N10" s="125">
         <f t="shared" si="7"/>
         <v>0.52674567584881493</v>
       </c>
@@ -21087,17 +21511,17 @@
       <c r="A14" t="s">
         <v>208</v>
       </c>
-      <c r="J14" s="139"/>
-      <c r="K14" s="139"/>
-      <c r="L14" s="139">
+      <c r="J14" s="132"/>
+      <c r="K14" s="132"/>
+      <c r="L14" s="132">
         <f>L13/H13-1</f>
         <v>0.64136391313172325</v>
       </c>
-      <c r="M14" s="139">
+      <c r="M14" s="132">
         <f>M13/I13-1</f>
         <v>0.74182638105975185</v>
       </c>
-      <c r="N14" s="139">
+      <c r="N14" s="132">
         <f>N13/J13-1</f>
         <v>0.58705864524928009</v>
       </c>
@@ -21106,31 +21530,31 @@
       <c r="A16" t="s">
         <v>209</v>
       </c>
-      <c r="H16" s="139">
+      <c r="H16" s="132">
         <f>Model!P3/KPIs!H13</f>
         <v>9.5349368784250058E-2</v>
       </c>
-      <c r="I16" s="139">
+      <c r="I16" s="132">
         <f>Model!Q3/KPIs!I13</f>
         <v>0.10516442127019916</v>
       </c>
-      <c r="J16" s="139">
+      <c r="J16" s="132">
         <f>Model!R3/KPIs!J13</f>
         <v>0.10601256402485225</v>
       </c>
-      <c r="K16" s="139">
+      <c r="K16" s="132">
         <f>Model!S3/KPIs!K13</f>
         <v>0.1148270516717325</v>
       </c>
-      <c r="L16" s="139">
+      <c r="L16" s="132">
         <f>Model!T3/KPIs!L13</f>
         <v>0.12972919500432795</v>
       </c>
-      <c r="M16" s="139">
+      <c r="M16" s="132">
         <f>Model!U3/KPIs!M13</f>
         <v>0.10647464940668824</v>
       </c>
-      <c r="N16" s="139">
+      <c r="N16" s="132">
         <f>Model!V3/KPIs!N13</f>
         <v>0.11152105413921513</v>
       </c>
@@ -21195,13 +21619,13 @@
       <c r="A21" t="s">
         <v>211</v>
       </c>
-      <c r="B21" s="140">
+      <c r="B21" s="133">
         <v>5.5999999999999999E-3</v>
       </c>
-      <c r="C21" s="140">
+      <c r="C21" s="133">
         <v>8.8000000000000005E-3</v>
       </c>
-      <c r="D21" s="140">
+      <c r="D21" s="133">
         <v>2.18E-2</v>
       </c>
       <c r="E21" s="17">
@@ -21228,18 +21652,18 @@
         <f>E21/G21</f>
         <v>46.454545454545453</v>
       </c>
-      <c r="N21" s="130">
+      <c r="N21" s="125">
         <v>1</v>
       </c>
-      <c r="P21" s="130">
+      <c r="P21" s="125">
         <f>J21/I21-1</f>
         <v>0.28774928774928776</v>
       </c>
-      <c r="R21" s="141">
+      <c r="R21" s="134">
         <f>11567/I21</f>
         <v>3.2954415954415954</v>
       </c>
-      <c r="S21" s="141">
+      <c r="S21" s="134">
         <f>11567/J21</f>
         <v>2.5590707964601771</v>
       </c>
@@ -21248,7 +21672,7 @@
       <c r="A22" t="s">
         <v>218</v>
       </c>
-      <c r="C22" s="140">
+      <c r="C22" s="133">
         <v>2.4E-2</v>
       </c>
       <c r="E22">
@@ -21275,19 +21699,19 @@
         <f t="shared" ref="L22:L24" si="9">E22/G22</f>
         <v>17.783289817232376</v>
       </c>
-      <c r="N22" s="130">
+      <c r="N22" s="125">
         <f t="shared" ref="N22:N24" si="10">G22/F22-1</f>
         <v>0.23151125401929273</v>
       </c>
-      <c r="P22" s="130">
+      <c r="P22" s="125">
         <f t="shared" ref="P22:P24" si="11">J22/I22-1</f>
         <v>0.24019607843137258</v>
       </c>
-      <c r="R22" s="141">
+      <c r="R22" s="134">
         <f>22481/I22</f>
         <v>5.5100490196078429</v>
       </c>
-      <c r="S22" s="141">
+      <c r="S22" s="134">
         <f>22481/J22</f>
         <v>4.4428853754940709</v>
       </c>
@@ -21320,19 +21744,19 @@
         <f t="shared" si="9"/>
         <v>15.456621004566211</v>
       </c>
-      <c r="N23" s="130">
+      <c r="N23" s="125">
         <f t="shared" si="10"/>
         <v>0.29585798816568043</v>
       </c>
-      <c r="P23" s="130">
+      <c r="P23" s="125">
         <f t="shared" si="11"/>
         <v>0.2601522842639592</v>
       </c>
-      <c r="R23" s="141">
+      <c r="R23" s="134">
         <f>2312/I23</f>
         <v>5.1473862320776558</v>
       </c>
-      <c r="S23" s="141">
+      <c r="S23" s="134">
         <f>2312/J23</f>
         <v>4.0847334852741115</v>
       </c>
@@ -21365,19 +21789,19 @@
         <f t="shared" si="9"/>
         <v>10.494845360824742</v>
       </c>
-      <c r="N24" s="130">
+      <c r="N24" s="125">
         <f t="shared" si="10"/>
         <v>8.7850467289719791E-2</v>
       </c>
-      <c r="P24" s="130">
+      <c r="P24" s="125">
         <f t="shared" si="11"/>
         <v>5.9723889555822307E-2</v>
       </c>
-      <c r="R24" s="141">
+      <c r="R24" s="134">
         <f>58393/I24</f>
         <v>1.7524909963985593</v>
       </c>
-      <c r="S24" s="141">
+      <c r="S24" s="134">
         <f>58393/J24</f>
         <v>1.6537241574624753</v>
       </c>
@@ -29757,48 +30181,48 @@
       <c r="D1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="155" t="s">
+      <c r="H1" s="146" t="s">
         <v>84</v>
       </c>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="157"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="148"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D2" t="e">
         <f>C2/C3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H2" s="57"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="59"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="55"/>
     </row>
     <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D3" t="e">
         <f t="shared" ref="D3:D66" si="0">C3/C4-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H3" s="60" t="s">
+      <c r="H3" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="I3" s="61" t="s">
+      <c r="I3" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="J3" s="62" t="s">
+      <c r="J3" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="K3" s="63" t="s">
+      <c r="K3" s="59" t="s">
         <v>88</v>
       </c>
-      <c r="L3" s="63" t="s">
+      <c r="L3" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="M3" s="64" t="s">
+      <c r="M3" s="60" t="s">
         <v>90</v>
       </c>
     </row>
@@ -29807,27 +30231,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H4" s="65" t="e">
+      <c r="H4" s="61" t="e">
         <f>$I$19-3*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I4" s="66" t="e">
+      <c r="I4" s="62" t="e">
         <f>H4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J4" s="67">
+      <c r="J4" s="63">
         <f>COUNTIF(D:D,"&lt;="&amp;H4)</f>
         <v>67</v>
       </c>
-      <c r="K4" s="67" t="e">
+      <c r="K4" s="63" t="e">
         <f>"Less than "&amp;TEXT(H4,"0,00%")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L4" s="68" t="e">
+      <c r="L4" s="64" t="e">
         <f>J4/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M4" s="69" t="e">
+      <c r="M4" s="65" t="e">
         <f>L4</f>
         <v>#DIV/0!</v>
       </c>
@@ -29837,27 +30261,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H5" s="70" t="e">
+      <c r="H5" s="66" t="e">
         <f>$I$19-2.4*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I5" s="71" t="e">
+      <c r="I5" s="67" t="e">
         <f>H5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J5" s="72">
+      <c r="J5" s="68">
         <f>COUNTIFS(D:D,"&lt;="&amp;H5,D:D,"&gt;"&amp;H4)</f>
         <v>67</v>
       </c>
-      <c r="K5" s="73" t="e">
+      <c r="K5" s="69" t="e">
         <f t="shared" ref="K5:K14" si="1">TEXT(H4,"0,00%")&amp;" to "&amp;TEXT(H5,"0,00%")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L5" s="74" t="e">
+      <c r="L5" s="70" t="e">
         <f>J5/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M5" s="75" t="e">
+      <c r="M5" s="71" t="e">
         <f>M4+L5</f>
         <v>#DIV/0!</v>
       </c>
@@ -29867,27 +30291,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H6" s="70" t="e">
+      <c r="H6" s="66" t="e">
         <f>$I$19-1.8*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I6" s="71" t="e">
+      <c r="I6" s="67" t="e">
         <f t="shared" ref="I6:I14" si="2">H6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J6" s="72">
+      <c r="J6" s="68">
         <f t="shared" ref="J6:J14" si="3">COUNTIFS(D:D,"&lt;="&amp;H6,D:D,"&gt;"&amp;H5)</f>
         <v>67</v>
       </c>
-      <c r="K6" s="73" t="e">
+      <c r="K6" s="69" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L6" s="74" t="e">
+      <c r="L6" s="70" t="e">
         <f t="shared" ref="L6:L15" si="4">J6/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M6" s="75" t="e">
+      <c r="M6" s="71" t="e">
         <f t="shared" ref="M6:M15" si="5">M5+L6</f>
         <v>#DIV/0!</v>
       </c>
@@ -29897,27 +30321,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H7" s="70" t="e">
+      <c r="H7" s="66" t="e">
         <f>$I$19-1.2*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I7" s="71" t="e">
+      <c r="I7" s="67" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="68">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K7" s="73" t="e">
+      <c r="K7" s="69" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L7" s="74" t="e">
+      <c r="L7" s="70" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M7" s="75" t="e">
+      <c r="M7" s="71" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -29927,27 +30351,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H8" s="70" t="e">
+      <c r="H8" s="66" t="e">
         <f>$I$19-0.6*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I8" s="71" t="e">
+      <c r="I8" s="67" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J8" s="72">
+      <c r="J8" s="68">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K8" s="73" t="e">
+      <c r="K8" s="69" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L8" s="74" t="e">
+      <c r="L8" s="70" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M8" s="75" t="e">
+      <c r="M8" s="71" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -29957,27 +30381,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H9" s="70" t="e">
+      <c r="H9" s="66" t="e">
         <f>$I$19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I9" s="71" t="e">
+      <c r="I9" s="67" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J9" s="72">
+      <c r="J9" s="68">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K9" s="73" t="e">
+      <c r="K9" s="69" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L9" s="74" t="e">
+      <c r="L9" s="70" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M9" s="75" t="e">
+      <c r="M9" s="71" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -29987,27 +30411,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H10" s="70" t="e">
+      <c r="H10" s="66" t="e">
         <f>$I$19+0.6*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I10" s="71" t="e">
+      <c r="I10" s="67" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J10" s="72">
+      <c r="J10" s="68">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K10" s="73" t="e">
+      <c r="K10" s="69" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L10" s="74" t="e">
+      <c r="L10" s="70" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M10" s="75" t="e">
+      <c r="M10" s="71" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -30017,27 +30441,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H11" s="70" t="e">
+      <c r="H11" s="66" t="e">
         <f>$I$19+1.2*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I11" s="71" t="e">
+      <c r="I11" s="67" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J11" s="72">
+      <c r="J11" s="68">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K11" s="73" t="e">
+      <c r="K11" s="69" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L11" s="74" t="e">
+      <c r="L11" s="70" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M11" s="75" t="e">
+      <c r="M11" s="71" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -30047,27 +30471,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H12" s="70" t="e">
+      <c r="H12" s="66" t="e">
         <f>$I$19+1.8*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I12" s="71" t="e">
+      <c r="I12" s="67" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J12" s="72">
+      <c r="J12" s="68">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K12" s="73" t="e">
+      <c r="K12" s="69" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L12" s="74" t="e">
+      <c r="L12" s="70" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M12" s="75" t="e">
+      <c r="M12" s="71" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -30077,27 +30501,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H13" s="70" t="e">
+      <c r="H13" s="66" t="e">
         <f>$I$19+2.4*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I13" s="71" t="e">
+      <c r="I13" s="67" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J13" s="72">
+      <c r="J13" s="68">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K13" s="73" t="e">
+      <c r="K13" s="69" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L13" s="74" t="e">
+      <c r="L13" s="70" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M13" s="75" t="e">
+      <c r="M13" s="71" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -30107,27 +30531,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H14" s="70" t="e">
+      <c r="H14" s="66" t="e">
         <f>$I$19+3*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I14" s="71" t="e">
+      <c r="I14" s="67" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J14" s="72">
+      <c r="J14" s="68">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K14" s="73" t="e">
+      <c r="K14" s="69" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L14" s="74" t="e">
+      <c r="L14" s="70" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M14" s="75" t="e">
+      <c r="M14" s="71" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -30137,23 +30561,23 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H15" s="76"/>
-      <c r="I15" s="77" t="s">
+      <c r="H15" s="72"/>
+      <c r="I15" s="73" t="s">
         <v>91</v>
       </c>
-      <c r="J15" s="77">
+      <c r="J15" s="73">
         <f>COUNTIF(D:D,"&gt;"&amp;H14)</f>
         <v>67</v>
       </c>
-      <c r="K15" s="77" t="e">
+      <c r="K15" s="73" t="e">
         <f>"Greater than "&amp;TEXT(H14,"0,00%")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L15" s="78" t="e">
+      <c r="L15" s="74" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M15" s="78" t="e">
+      <c r="M15" s="74" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -30163,349 +30587,349 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H16" s="79"/>
-      <c r="M16" s="80"/>
+      <c r="H16" s="75"/>
+      <c r="M16" s="76"/>
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D17" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H17" s="158" t="s">
+      <c r="H17" s="149" t="s">
         <v>122</v>
       </c>
-      <c r="I17" s="159"/>
-      <c r="M17" s="80"/>
+      <c r="I17" s="150"/>
+      <c r="M17" s="76"/>
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H18" s="160"/>
-      <c r="I18" s="161"/>
-      <c r="M18" s="80"/>
+      <c r="H18" s="151"/>
+      <c r="I18" s="152"/>
+      <c r="M18" s="76"/>
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D19" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H19" s="81" t="s">
+      <c r="H19" s="77" t="s">
         <v>92</v>
       </c>
-      <c r="I19" s="117" t="e">
+      <c r="I19" s="113" t="e">
         <f>AVERAGE(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M19" s="80"/>
+      <c r="M19" s="76"/>
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D20" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H20" s="81" t="s">
+      <c r="H20" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="I20" s="117" t="e">
+      <c r="I20" s="113" t="e">
         <f>_xlfn.STDEV.S(D:D)/SQRT(COUNT(D:D))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M20" s="80"/>
+      <c r="M20" s="76"/>
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D21" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H21" s="81" t="s">
+      <c r="H21" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="I21" s="117" t="e">
+      <c r="I21" s="113" t="e">
         <f>MEDIAN(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M21" s="80"/>
+      <c r="M21" s="76"/>
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D22" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H22" s="81" t="s">
+      <c r="H22" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="I22" s="117" t="e">
+      <c r="I22" s="113" t="e">
         <f>MODE(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M22" s="80"/>
+      <c r="M22" s="76"/>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D23" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H23" s="81" t="s">
+      <c r="H23" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="I23" s="117" t="e">
+      <c r="I23" s="113" t="e">
         <f>_xlfn.STDEV.S(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M23" s="80"/>
+      <c r="M23" s="76"/>
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D24" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H24" s="81" t="s">
+      <c r="H24" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="I24" s="117" t="e">
+      <c r="I24" s="113" t="e">
         <f>_xlfn.VAR.S(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M24" s="80"/>
+      <c r="M24" s="76"/>
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D25" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H25" s="81" t="s">
+      <c r="H25" s="77" t="s">
         <v>98</v>
       </c>
-      <c r="I25" s="118" t="e">
+      <c r="I25" s="114" t="e">
         <f>KURT(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M25" s="80"/>
+      <c r="M25" s="76"/>
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D26" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H26" s="81" t="s">
+      <c r="H26" s="77" t="s">
         <v>99</v>
       </c>
-      <c r="I26" s="118" t="e">
+      <c r="I26" s="114" t="e">
         <f>SKEW(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M26" s="80"/>
+      <c r="M26" s="76"/>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D27" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H27" s="81" t="s">
+      <c r="H27" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="I27" s="117" t="e">
+      <c r="I27" s="113" t="e">
         <f>I29-I28</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M27" s="80"/>
+      <c r="M27" s="76"/>
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D28" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H28" s="81" t="s">
+      <c r="H28" s="77" t="s">
         <v>100</v>
       </c>
-      <c r="I28" s="117" t="e">
+      <c r="I28" s="113" t="e">
         <f>MIN(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M28" s="80"/>
+      <c r="M28" s="76"/>
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D29" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H29" s="81" t="s">
+      <c r="H29" s="77" t="s">
         <v>101</v>
       </c>
-      <c r="I29" s="117" t="e">
+      <c r="I29" s="113" t="e">
         <f>MAX(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M29" s="80"/>
+      <c r="M29" s="76"/>
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H30" s="81" t="s">
+      <c r="H30" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="I30" s="118" t="e">
+      <c r="I30" s="114" t="e">
         <f>SUM(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M30" s="80"/>
+      <c r="M30" s="76"/>
     </row>
     <row r="31" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D31" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H31" s="82" t="s">
+      <c r="H31" s="78" t="s">
         <v>103</v>
       </c>
-      <c r="I31" s="59">
+      <c r="I31" s="55">
         <f>COUNT(D:D)</f>
         <v>0</v>
       </c>
-      <c r="M31" s="80"/>
+      <c r="M31" s="76"/>
     </row>
     <row r="32" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D32" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H32" s="84"/>
-      <c r="M32" s="80"/>
+      <c r="H32" s="80"/>
+      <c r="M32" s="76"/>
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D33" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H33" s="85"/>
-      <c r="I33" s="86" t="s">
+      <c r="H33" s="81"/>
+      <c r="I33" s="82" t="s">
         <v>104</v>
       </c>
-      <c r="J33" s="86" t="s">
+      <c r="J33" s="82" t="s">
         <v>103</v>
       </c>
-      <c r="K33" s="86" t="s">
+      <c r="K33" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="L33" s="87" t="s">
+      <c r="L33" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="M33" s="80"/>
+      <c r="M33" s="76"/>
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D34" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H34" s="88" t="s">
+      <c r="H34" s="84" t="s">
         <v>107</v>
       </c>
-      <c r="I34" s="74" t="e">
+      <c r="I34" s="70" t="e">
         <f>AVERAGEIF(D:D,"&gt;0")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J34" s="72">
+      <c r="J34" s="68">
         <f>COUNTIF(D:D,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="K34" s="74" t="e">
+      <c r="K34" s="70" t="e">
         <f>J34/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L34" s="75" t="e">
+      <c r="L34" s="71" t="e">
         <f>K34*I34</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M34" s="80"/>
+      <c r="M34" s="76"/>
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D35" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H35" s="88" t="s">
+      <c r="H35" s="84" t="s">
         <v>108</v>
       </c>
-      <c r="I35" s="74" t="e">
+      <c r="I35" s="70" t="e">
         <f>AVERAGEIF(D:D,"&lt;0")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J35" s="72">
+      <c r="J35" s="68">
         <f>COUNTIF(D:D,"&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="K35" s="74" t="e">
+      <c r="K35" s="70" t="e">
         <f>J35/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L35" s="75" t="e">
+      <c r="L35" s="71" t="e">
         <f t="shared" ref="L35:L36" si="6">K35*I35</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M35" s="80"/>
+      <c r="M35" s="76"/>
     </row>
     <row r="36" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D36" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H36" s="89" t="s">
+      <c r="H36" s="85" t="s">
         <v>109</v>
       </c>
-      <c r="I36" s="77">
+      <c r="I36" s="73">
         <v>0</v>
       </c>
-      <c r="J36" s="77">
+      <c r="J36" s="73">
         <f>COUNTIF(D:D,"0")</f>
         <v>0</v>
       </c>
-      <c r="K36" s="90" t="e">
+      <c r="K36" s="86" t="e">
         <f>J36/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L36" s="78" t="e">
+      <c r="L36" s="74" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M36" s="80"/>
+      <c r="M36" s="76"/>
     </row>
     <row r="37" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D37" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H37" s="84"/>
-      <c r="I37" s="91"/>
-      <c r="J37" s="91"/>
-      <c r="K37" s="91"/>
-      <c r="L37" s="91"/>
-      <c r="M37" s="80"/>
+      <c r="H37" s="80"/>
+      <c r="I37" s="87"/>
+      <c r="J37" s="87"/>
+      <c r="K37" s="87"/>
+      <c r="L37" s="87"/>
+      <c r="M37" s="76"/>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D38" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H38" s="65" t="s">
+      <c r="H38" s="61" t="s">
         <v>110</v>
       </c>
-      <c r="I38" s="86" t="s">
+      <c r="I38" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="J38" s="86" t="s">
+      <c r="J38" s="82" t="s">
         <v>112</v>
       </c>
-      <c r="K38" s="86" t="s">
+      <c r="K38" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="L38" s="86" t="s">
+      <c r="L38" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="M38" s="87" t="s">
+      <c r="M38" s="83" t="s">
         <v>115</v>
       </c>
     </row>
@@ -30514,26 +30938,26 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H39" s="92">
+      <c r="H39" s="88">
         <v>1</v>
       </c>
-      <c r="I39" s="74" t="e">
+      <c r="I39" s="70" t="e">
         <f>$I$19+($H39*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J39" s="74" t="e">
+      <c r="J39" s="70" t="e">
         <f>$I$19-($H39*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K39" s="72">
+      <c r="K39" s="68">
         <f>COUNTIFS(D:D,"&lt;"&amp;I39,D:D,"&gt;"&amp;J39)</f>
         <v>67</v>
       </c>
-      <c r="L39" s="74" t="e">
+      <c r="L39" s="70" t="e">
         <f>K39/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M39" s="75">
+      <c r="M39" s="71">
         <v>0.68269999999999997</v>
       </c>
     </row>
@@ -30542,26 +30966,26 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H40" s="92">
+      <c r="H40" s="88">
         <v>2</v>
       </c>
-      <c r="I40" s="74" t="e">
+      <c r="I40" s="70" t="e">
         <f>$I$19+($H40*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J40" s="74" t="e">
+      <c r="J40" s="70" t="e">
         <f>$I$19-($H40*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K40" s="72">
+      <c r="K40" s="68">
         <f>COUNTIFS(D:D,"&lt;"&amp;I40,D:D,"&gt;"&amp;J40)</f>
         <v>67</v>
       </c>
-      <c r="L40" s="74" t="e">
+      <c r="L40" s="70" t="e">
         <f>K40/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M40" s="75">
+      <c r="M40" s="71">
         <v>0.95450000000000002</v>
       </c>
     </row>
@@ -30570,26 +30994,26 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H41" s="92">
+      <c r="H41" s="88">
         <v>3</v>
       </c>
-      <c r="I41" s="74" t="e">
+      <c r="I41" s="70" t="e">
         <f>$I$19+($H41*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="74" t="e">
+      <c r="J41" s="70" t="e">
         <f>$I$19-($H41*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K41" s="72">
+      <c r="K41" s="68">
         <f>COUNTIFS(D:D,"&lt;"&amp;I41,D:D,"&gt;"&amp;J41)</f>
         <v>67</v>
       </c>
-      <c r="L41" s="74" t="e">
+      <c r="L41" s="70" t="e">
         <f>K41/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M41" s="93">
+      <c r="M41" s="89">
         <v>0.99729999999999996</v>
       </c>
     </row>
@@ -30598,46 +31022,46 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H42" s="70"/>
-      <c r="M42" s="93"/>
+      <c r="H42" s="66"/>
+      <c r="M42" s="89"/>
     </row>
     <row r="43" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D43" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H43" s="162" t="s">
+      <c r="H43" s="153" t="s">
         <v>116</v>
       </c>
-      <c r="I43" s="163"/>
-      <c r="J43" s="163"/>
-      <c r="K43" s="163"/>
-      <c r="L43" s="163"/>
-      <c r="M43" s="164"/>
+      <c r="I43" s="154"/>
+      <c r="J43" s="154"/>
+      <c r="K43" s="154"/>
+      <c r="L43" s="154"/>
+      <c r="M43" s="155"/>
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D44" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H44" s="94">
+      <c r="H44" s="90">
         <v>0.01</v>
       </c>
-      <c r="I44" s="95" t="e">
+      <c r="I44" s="91" t="e">
         <f t="shared" ref="I44:I58" si="7">_xlfn.PERCENTILE.INC(D:D,H44)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J44" s="96">
+      <c r="J44" s="92">
         <v>0.2</v>
       </c>
-      <c r="K44" s="95" t="e">
+      <c r="K44" s="91" t="e">
         <f t="shared" ref="K44:K56" si="8">_xlfn.PERCENTILE.INC(D:D,J44)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L44" s="96">
+      <c r="L44" s="92">
         <v>0.85</v>
       </c>
-      <c r="M44" s="97" t="e">
+      <c r="M44" s="93" t="e">
         <f t="shared" ref="M44:M58" si="9">_xlfn.PERCENTILE.INC(D:D,L44)</f>
         <v>#DIV/0!</v>
       </c>
@@ -30647,24 +31071,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H45" s="98">
+      <c r="H45" s="94">
         <v>0.02</v>
       </c>
-      <c r="I45" s="99" t="e">
+      <c r="I45" s="95" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J45" s="100">
+      <c r="J45" s="96">
         <v>0.25</v>
       </c>
-      <c r="K45" s="99" t="e">
+      <c r="K45" s="95" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L45" s="100">
+      <c r="L45" s="96">
         <v>0.86</v>
       </c>
-      <c r="M45" s="101" t="e">
+      <c r="M45" s="97" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -30674,24 +31098,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H46" s="98">
+      <c r="H46" s="94">
         <v>0.03</v>
       </c>
-      <c r="I46" s="99" t="e">
+      <c r="I46" s="95" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J46" s="100">
+      <c r="J46" s="96">
         <v>0.3</v>
       </c>
-      <c r="K46" s="99" t="e">
+      <c r="K46" s="95" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L46" s="100">
+      <c r="L46" s="96">
         <v>0.87</v>
       </c>
-      <c r="M46" s="101" t="e">
+      <c r="M46" s="97" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -30701,24 +31125,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H47" s="98">
+      <c r="H47" s="94">
         <v>0.04</v>
       </c>
-      <c r="I47" s="99" t="e">
+      <c r="I47" s="95" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J47" s="100">
+      <c r="J47" s="96">
         <v>0.35</v>
       </c>
-      <c r="K47" s="99" t="e">
+      <c r="K47" s="95" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L47" s="100">
+      <c r="L47" s="96">
         <v>0.88</v>
       </c>
-      <c r="M47" s="101" t="e">
+      <c r="M47" s="97" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -30728,24 +31152,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H48" s="98">
+      <c r="H48" s="94">
         <v>0.05</v>
       </c>
-      <c r="I48" s="99" t="e">
+      <c r="I48" s="95" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J48" s="100">
+      <c r="J48" s="96">
         <v>0.4</v>
       </c>
-      <c r="K48" s="99" t="e">
+      <c r="K48" s="95" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L48" s="100">
+      <c r="L48" s="96">
         <v>0.89</v>
       </c>
-      <c r="M48" s="101" t="e">
+      <c r="M48" s="97" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -30755,24 +31179,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H49" s="98">
+      <c r="H49" s="94">
         <v>0.06</v>
       </c>
-      <c r="I49" s="99" t="e">
+      <c r="I49" s="95" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J49" s="100">
+      <c r="J49" s="96">
         <v>0.45</v>
       </c>
-      <c r="K49" s="99" t="e">
+      <c r="K49" s="95" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L49" s="100">
+      <c r="L49" s="96">
         <v>0.9</v>
       </c>
-      <c r="M49" s="101" t="e">
+      <c r="M49" s="97" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -30782,24 +31206,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H50" s="98">
+      <c r="H50" s="94">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I50" s="99" t="e">
+      <c r="I50" s="95" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J50" s="100">
+      <c r="J50" s="96">
         <v>0.5</v>
       </c>
-      <c r="K50" s="99" t="e">
+      <c r="K50" s="95" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L50" s="100">
+      <c r="L50" s="96">
         <v>0.91</v>
       </c>
-      <c r="M50" s="101" t="e">
+      <c r="M50" s="97" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -30809,24 +31233,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H51" s="98">
+      <c r="H51" s="94">
         <v>0.08</v>
       </c>
-      <c r="I51" s="99" t="e">
+      <c r="I51" s="95" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J51" s="100">
+      <c r="J51" s="96">
         <v>0.55000000000000004</v>
       </c>
-      <c r="K51" s="99" t="e">
+      <c r="K51" s="95" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L51" s="100">
+      <c r="L51" s="96">
         <v>0.92</v>
       </c>
-      <c r="M51" s="101" t="e">
+      <c r="M51" s="97" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -30836,24 +31260,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H52" s="98">
+      <c r="H52" s="94">
         <v>0.09</v>
       </c>
-      <c r="I52" s="99" t="e">
+      <c r="I52" s="95" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J52" s="100">
+      <c r="J52" s="96">
         <v>0.6</v>
       </c>
-      <c r="K52" s="99" t="e">
+      <c r="K52" s="95" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L52" s="100">
+      <c r="L52" s="96">
         <v>0.93</v>
       </c>
-      <c r="M52" s="101" t="e">
+      <c r="M52" s="97" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -30863,24 +31287,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H53" s="98">
+      <c r="H53" s="94">
         <v>0.1</v>
       </c>
-      <c r="I53" s="99" t="e">
+      <c r="I53" s="95" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J53" s="100">
+      <c r="J53" s="96">
         <v>0.65</v>
       </c>
-      <c r="K53" s="99" t="e">
+      <c r="K53" s="95" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L53" s="100">
+      <c r="L53" s="96">
         <v>0.94</v>
       </c>
-      <c r="M53" s="101" t="e">
+      <c r="M53" s="97" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -30890,24 +31314,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H54" s="98">
+      <c r="H54" s="94">
         <v>0.11</v>
       </c>
-      <c r="I54" s="99" t="e">
+      <c r="I54" s="95" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J54" s="100">
+      <c r="J54" s="96">
         <v>0.7</v>
       </c>
-      <c r="K54" s="99" t="e">
+      <c r="K54" s="95" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L54" s="100">
+      <c r="L54" s="96">
         <v>0.95</v>
       </c>
-      <c r="M54" s="101" t="e">
+      <c r="M54" s="97" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -30917,24 +31341,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H55" s="98">
+      <c r="H55" s="94">
         <v>0.12</v>
       </c>
-      <c r="I55" s="99" t="e">
+      <c r="I55" s="95" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J55" s="100">
+      <c r="J55" s="96">
         <v>0.75</v>
       </c>
-      <c r="K55" s="99" t="e">
+      <c r="K55" s="95" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L55" s="100">
+      <c r="L55" s="96">
         <v>0.96</v>
       </c>
-      <c r="M55" s="101" t="e">
+      <c r="M55" s="97" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -30944,24 +31368,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H56" s="98">
+      <c r="H56" s="94">
         <v>0.13</v>
       </c>
-      <c r="I56" s="99" t="e">
+      <c r="I56" s="95" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J56" s="100">
+      <c r="J56" s="96">
         <v>0.8</v>
       </c>
-      <c r="K56" s="99" t="e">
+      <c r="K56" s="95" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L56" s="100">
+      <c r="L56" s="96">
         <v>0.97</v>
       </c>
-      <c r="M56" s="101" t="e">
+      <c r="M56" s="97" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -30971,19 +31395,19 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H57" s="98">
+      <c r="H57" s="94">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I57" s="99" t="e">
+      <c r="I57" s="95" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J57" s="100"/>
-      <c r="K57" s="99"/>
-      <c r="L57" s="100">
+      <c r="J57" s="96"/>
+      <c r="K57" s="95"/>
+      <c r="L57" s="96">
         <v>0.98</v>
       </c>
-      <c r="M57" s="101" t="e">
+      <c r="M57" s="97" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -30993,19 +31417,19 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H58" s="102">
+      <c r="H58" s="98">
         <v>0.15</v>
       </c>
-      <c r="I58" s="103" t="e">
+      <c r="I58" s="99" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J58" s="104"/>
-      <c r="K58" s="83"/>
-      <c r="L58" s="105">
+      <c r="J58" s="100"/>
+      <c r="K58" s="79"/>
+      <c r="L58" s="101">
         <v>0.99</v>
       </c>
-      <c r="M58" s="106" t="e">
+      <c r="M58" s="102" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -31021,47 +31445,47 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H60" s="107" t="s">
+      <c r="H60" s="103" t="s">
         <v>117</v>
       </c>
-      <c r="I60" s="108"/>
+      <c r="I60" s="104"/>
     </row>
     <row r="61" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D61" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H61" s="109" t="s">
+      <c r="H61" s="105" t="s">
         <v>118</v>
       </c>
-      <c r="I61" s="110"/>
+      <c r="I61" s="106"/>
     </row>
     <row r="62" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D62" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H62" s="111"/>
+      <c r="H62" s="107"/>
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D63" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H63" s="107" t="s">
+      <c r="H63" s="103" t="s">
         <v>119</v>
       </c>
-      <c r="I63" s="112"/>
+      <c r="I63" s="108"/>
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D64" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H64" s="113" t="s">
+      <c r="H64" s="109" t="s">
         <v>120</v>
       </c>
-      <c r="I64" s="114">
+      <c r="I64" s="110">
         <f>I63*(1-I60)</f>
         <v>0</v>
       </c>
@@ -31071,10 +31495,10 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H65" s="109" t="s">
+      <c r="H65" s="105" t="s">
         <v>121</v>
       </c>
-      <c r="I65" s="115">
+      <c r="I65" s="111">
         <f>I63*(1+I61)</f>
         <v>0</v>
       </c>
